--- a/empirical/realized_shocks_Finland.xlsx
+++ b/empirical/realized_shocks_Finland.xlsx
@@ -131,7 +131,7 @@
         <v>191304</v>
       </c>
       <c r="B7" s="1">
-        <v>0.15984377264976501</v>
+        <v>0.15984377264976502</v>
       </c>
       <c r="C7" s="1"/>
     </row>
@@ -158,7 +158,7 @@
         <v>191307</v>
       </c>
       <c r="B10" s="1">
-        <v>-0.055749166756868362</v>
+        <v>-0.055749166756868363</v>
       </c>
       <c r="C10" s="1"/>
     </row>
@@ -338,7 +338,7 @@
         <v>191503</v>
       </c>
       <c r="B30" s="1">
-        <v>-0.22664442658424377</v>
+        <v>-0.22664442658424378</v>
       </c>
       <c r="C30" s="1"/>
     </row>
@@ -1553,7 +1553,7 @@
         <v>192606</v>
       </c>
       <c r="B165" s="1">
-        <v>0.061351288110017776</v>
+        <v>0.061351288110017777</v>
       </c>
       <c r="C165" s="1"/>
     </row>
@@ -2327,7 +2327,7 @@
         <v>193308</v>
       </c>
       <c r="B251" s="1">
-        <v>0.22133003175258636</v>
+        <v>0.22133003175258637</v>
       </c>
       <c r="C251" s="1"/>
     </row>
@@ -2489,7 +2489,7 @@
         <v>193502</v>
       </c>
       <c r="B269" s="1">
-        <v>-0.061881732195615768</v>
+        <v>-0.061881732195615769</v>
       </c>
       <c r="C269" s="1"/>
     </row>
@@ -2570,7 +2570,7 @@
         <v>193511</v>
       </c>
       <c r="B278" s="1">
-        <v>0.018396457657217979</v>
+        <v>0.01839645765721798</v>
       </c>
       <c r="C278" s="1"/>
     </row>
@@ -2633,7 +2633,7 @@
         <v>193606</v>
       </c>
       <c r="B285" s="1">
-        <v>0.04342338815331459</v>
+        <v>0.043423388153314591</v>
       </c>
       <c r="C285" s="1"/>
     </row>
@@ -2813,7 +2813,7 @@
         <v>193802</v>
       </c>
       <c r="B305" s="1">
-        <v>-0.26365926861763</v>
+        <v>-0.26365926861763001</v>
       </c>
       <c r="C305" s="1"/>
     </row>
@@ -2993,7 +2993,7 @@
         <v>193910</v>
       </c>
       <c r="B325" s="1">
-        <v>-0.24601979553699493</v>
+        <v>-0.24601979553699494</v>
       </c>
       <c r="C325" s="1"/>
     </row>
@@ -3002,7 +3002,7 @@
         <v>193911</v>
       </c>
       <c r="B326" s="1">
-        <v>-0.16898398101329803</v>
+        <v>-0.16898398101329804</v>
       </c>
       <c r="C326" s="1"/>
     </row>
@@ -3083,7 +3083,7 @@
         <v>194008</v>
       </c>
       <c r="B335" s="1">
-        <v>0.15131391584873199</v>
+        <v>0.151313915848732</v>
       </c>
       <c r="C335" s="1"/>
     </row>
@@ -3164,7 +3164,7 @@
         <v>194105</v>
       </c>
       <c r="B344" s="1">
-        <v>-0.20690621435642242</v>
+        <v>-0.20690621435642243</v>
       </c>
       <c r="C344" s="1"/>
     </row>
@@ -3362,7 +3362,7 @@
         <v>194303</v>
       </c>
       <c r="B366" s="1">
-        <v>0.077430188655853271</v>
+        <v>0.077430188655853272</v>
       </c>
       <c r="C366" s="1"/>
     </row>
@@ -3713,7 +3713,7 @@
         <v>194606</v>
       </c>
       <c r="B405" s="1">
-        <v>-0.43270868062973022</v>
+        <v>-0.43270868062973023</v>
       </c>
       <c r="C405" s="1"/>
     </row>
@@ -3749,7 +3749,7 @@
         <v>194610</v>
       </c>
       <c r="B409" s="1">
-        <v>0.32130813598632812</v>
+        <v>0.32130813598632813</v>
       </c>
       <c r="C409" s="1"/>
     </row>
@@ -3812,7 +3812,7 @@
         <v>194705</v>
       </c>
       <c r="B416" s="1">
-        <v>-0.047184187918901443</v>
+        <v>-0.047184187918901444</v>
       </c>
       <c r="C416" s="1"/>
     </row>
@@ -3893,7 +3893,7 @@
         <v>194802</v>
       </c>
       <c r="B425" s="1">
-        <v>-0.74843358993530273</v>
+        <v>-0.74843358993530274</v>
       </c>
       <c r="C425" s="1"/>
     </row>
@@ -4064,7 +4064,7 @@
         <v>194909</v>
       </c>
       <c r="B444" s="1">
-        <v>-0.13582190871238708</v>
+        <v>-0.13582190871238709</v>
       </c>
       <c r="C444" s="1"/>
     </row>
@@ -4181,7 +4181,7 @@
         <v>195010</v>
       </c>
       <c r="B457" s="1">
-        <v>0.43542629480361938</v>
+        <v>0.43542629480361939</v>
       </c>
       <c r="C457" s="1"/>
     </row>
@@ -4253,7 +4253,7 @@
         <v>195106</v>
       </c>
       <c r="B465" s="1">
-        <v>0.039062850177288055</v>
+        <v>0.039062850177288056</v>
       </c>
       <c r="C465" s="1"/>
     </row>
@@ -4316,7 +4316,7 @@
         <v>195201</v>
       </c>
       <c r="B472" s="1">
-        <v>0.052806567400693893</v>
+        <v>0.052806567400693894</v>
       </c>
       <c r="C472" s="1"/>
     </row>
@@ -4784,7 +4784,7 @@
         <v>195605</v>
       </c>
       <c r="B524" s="1">
-        <v>0.060736685991287231</v>
+        <v>0.060736685991287232</v>
       </c>
       <c r="C524" s="1"/>
     </row>
@@ -4793,7 +4793,7 @@
         <v>195606</v>
       </c>
       <c r="B525" s="1">
-        <v>0.029304733499884605</v>
+        <v>0.029304733499884606</v>
       </c>
       <c r="C525" s="1"/>
     </row>
@@ -4847,7 +4847,7 @@
         <v>195612</v>
       </c>
       <c r="B531" s="1">
-        <v>-0.15450474619865417</v>
+        <v>-0.15450474619865418</v>
       </c>
       <c r="C531" s="1"/>
     </row>
@@ -5027,7 +5027,7 @@
         <v>195808</v>
       </c>
       <c r="B551" s="1">
-        <v>-0.041703693568706512</v>
+        <v>-0.041703693568706513</v>
       </c>
       <c r="C551" s="1"/>
     </row>
@@ -5522,7 +5522,7 @@
         <v>196303</v>
       </c>
       <c r="B606" s="1">
-        <v>0.087687030434608459</v>
+        <v>0.08768703043460846</v>
       </c>
       <c r="C606" s="1"/>
     </row>
@@ -5684,7 +5684,7 @@
         <v>196409</v>
       </c>
       <c r="B624" s="1">
-        <v>-0.18160636723041534</v>
+        <v>-0.18160636723041535</v>
       </c>
       <c r="C624" s="1"/>
     </row>
@@ -6134,7 +6134,7 @@
         <v>196811</v>
       </c>
       <c r="B674" s="1">
-        <v>-0.095804020762443542</v>
+        <v>-0.095804020762443543</v>
       </c>
       <c r="C674" s="1"/>
     </row>
@@ -6170,7 +6170,7 @@
         <v>196903</v>
       </c>
       <c r="B678" s="1">
-        <v>-0.090576328337192535</v>
+        <v>-0.090576328337192536</v>
       </c>
       <c r="C678" s="1"/>
     </row>
@@ -6206,7 +6206,7 @@
         <v>196907</v>
       </c>
       <c r="B682" s="1">
-        <v>-0.0040583051741123199</v>
+        <v>-0.00405830517411232</v>
       </c>
       <c r="C682" s="1"/>
     </row>
@@ -6341,7 +6341,7 @@
         <v>197010</v>
       </c>
       <c r="B697" s="1">
-        <v>0.079689569771289825</v>
+        <v>0.079689569771289826</v>
       </c>
       <c r="C697" s="1"/>
     </row>
@@ -6467,7 +6467,7 @@
         <v>197112</v>
       </c>
       <c r="B711" s="1">
-        <v>0.08407236635684967</v>
+        <v>0.084072366356849671</v>
       </c>
       <c r="C711" s="1"/>
     </row>
@@ -6584,7 +6584,7 @@
         <v>197301</v>
       </c>
       <c r="B724" s="1">
-        <v>0.78093636035919189</v>
+        <v>0.7809363603591919</v>
       </c>
       <c r="C724" s="1"/>
     </row>
@@ -6746,7 +6746,7 @@
         <v>197407</v>
       </c>
       <c r="B742" s="1">
-        <v>0.13666586577892303</v>
+        <v>0.13666586577892304</v>
       </c>
       <c r="C742" s="1"/>
     </row>
@@ -6791,7 +6791,7 @@
         <v>197412</v>
       </c>
       <c r="B747" s="1">
-        <v>0.045601185411214828</v>
+        <v>0.045601185411214829</v>
       </c>
       <c r="C747" s="1"/>
     </row>
@@ -7295,7 +7295,7 @@
         <v>197908</v>
       </c>
       <c r="B803" s="1">
-        <v>0.086994223296642303</v>
+        <v>0.086994223296642304</v>
       </c>
       <c r="C803" s="1"/>
     </row>
@@ -7421,7 +7421,7 @@
         <v>198010</v>
       </c>
       <c r="B817" s="1">
-        <v>-0.16964262723922729</v>
+        <v>-0.1696426272392273</v>
       </c>
       <c r="C817" s="1"/>
     </row>
@@ -7439,7 +7439,7 @@
         <v>198012</v>
       </c>
       <c r="B819" s="1">
-        <v>0.086994223296642303</v>
+        <v>0.086994223296642304</v>
       </c>
       <c r="C819" s="1"/>
     </row>
@@ -7466,7 +7466,7 @@
         <v>198103</v>
       </c>
       <c r="B822" s="1">
-        <v>0.08115050196647644</v>
+        <v>0.081150501966476441</v>
       </c>
       <c r="C822" s="1"/>
     </row>
@@ -7583,7 +7583,7 @@
         <v>198204</v>
       </c>
       <c r="B835" s="1">
-        <v>0.023687224835157394</v>
+        <v>0.023687224835157395</v>
       </c>
       <c r="C835" s="1"/>
     </row>
@@ -7700,7 +7700,7 @@
         <v>198305</v>
       </c>
       <c r="B848" s="1">
-        <v>0.24087893962860107</v>
+        <v>0.24087893962860108</v>
       </c>
       <c r="C848" s="1"/>
     </row>
@@ -7826,7 +7826,7 @@
         <v>198407</v>
       </c>
       <c r="B862" s="1">
-        <v>-0.12727563083171844</v>
+        <v>-0.12727563083171845</v>
       </c>
       <c r="C862" s="1"/>
     </row>
@@ -8015,7 +8015,7 @@
         <v>198604</v>
       </c>
       <c r="B883" s="1">
-        <v>0.64020001888275146</v>
+        <v>0.64020001888275147</v>
       </c>
       <c r="C883" s="1"/>
     </row>
@@ -8150,7 +8150,7 @@
         <v>198707</v>
       </c>
       <c r="B898" s="1">
-        <v>0.35921433568000793</v>
+        <v>0.35921433568000794</v>
       </c>
       <c r="C898" s="1"/>
     </row>
@@ -8159,7 +8159,7 @@
         <v>198708</v>
       </c>
       <c r="B899" s="1">
-        <v>0.08115050196647644</v>
+        <v>0.081150501966476441</v>
       </c>
       <c r="C899" s="1"/>
     </row>
@@ -8215,9 +8215,7 @@
       <c r="B905" s="1">
         <v>0.099655628204345703</v>
       </c>
-      <c r="C905" s="1">
-        <v>0.25378960371017456</v>
-      </c>
+      <c r="C905" s="1"/>
     </row>
     <row r="906">
       <c r="A906" s="1">
@@ -8227,7 +8225,7 @@
         <v>0.23406125605106354</v>
       </c>
       <c r="C906" s="1">
-        <v>-0.079856343567371368</v>
+        <v>-0.19141185283660889</v>
       </c>
     </row>
     <row r="907">
@@ -8238,7 +8236,7 @@
         <v>0.13861379027366638</v>
       </c>
       <c r="C907" s="1">
-        <v>-0.12340161204338074</v>
+        <v>-0.31206074357032776</v>
       </c>
     </row>
     <row r="908">
@@ -8249,7 +8247,7 @@
         <v>0.34898784756660461</v>
       </c>
       <c r="C908" s="1">
-        <v>0.090864129364490509</v>
+        <v>-0.091936863958835602</v>
       </c>
     </row>
     <row r="909">
@@ -8260,7 +8258,7 @@
         <v>0.22042590379714966</v>
       </c>
       <c r="C909" s="1">
-        <v>0.20026807487010956</v>
+        <v>0.12761105597019196</v>
       </c>
     </row>
     <row r="910">
@@ -8271,7 +8269,7 @@
         <v>0.096733763813972473</v>
       </c>
       <c r="C910" s="1">
-        <v>1.5735257863998413</v>
+        <v>0.71716916561126709</v>
       </c>
     </row>
     <row r="911">
@@ -8282,7 +8280,7 @@
         <v>-0.27921244502067566</v>
       </c>
       <c r="C911" s="1">
-        <v>0.22667127847671509</v>
+        <v>0.2780744731426239</v>
       </c>
     </row>
     <row r="912">
@@ -8293,7 +8291,7 @@
         <v>-0.32060548663139343</v>
       </c>
       <c r="C912" s="1">
-        <v>-0.042798727750778198</v>
+        <v>-0.31971108913421631</v>
       </c>
     </row>
     <row r="913">
@@ -8304,7 +8302,7 @@
         <v>0.14348354935646057</v>
       </c>
       <c r="C913" s="1">
-        <v>-0.18701337277889252</v>
+        <v>-0.15061675012111664</v>
       </c>
     </row>
     <row r="914">
@@ -8315,7 +8313,7 @@
         <v>0.13763983547687531</v>
       </c>
       <c r="C914" s="1">
-        <v>-0.28460502624511719</v>
+        <v>-0.29310029745101929</v>
       </c>
     </row>
     <row r="915">
@@ -8326,7 +8324,7 @@
         <v>-0.16185100376605988</v>
       </c>
       <c r="C915" s="1">
-        <v>0.06351674348115921</v>
+        <v>-0.12556308507919312</v>
       </c>
     </row>
     <row r="916">
@@ -8337,7 +8335,7 @@
         <v>0.054366767406463623</v>
       </c>
       <c r="C916" s="1">
-        <v>0.20324809849262238</v>
+        <v>0.12217293679714203</v>
       </c>
     </row>
     <row r="917">
@@ -8348,7 +8346,7 @@
         <v>0.063619330525398254</v>
       </c>
       <c r="C917" s="1">
-        <v>0.14813046157360077</v>
+        <v>0.081697948276996613</v>
       </c>
     </row>
     <row r="918">
@@ -8359,7 +8357,7 @@
         <v>0.21506915986537933</v>
       </c>
       <c r="C918" s="1">
-        <v>0.030903443694114685</v>
+        <v>-0.28467631340026855</v>
       </c>
     </row>
     <row r="919">
@@ -8370,7 +8368,7 @@
         <v>0.054366767406463623</v>
       </c>
       <c r="C919" s="1">
-        <v>-0.0068948771804571152</v>
+        <v>-0.25962981581687927</v>
       </c>
     </row>
     <row r="920">
@@ -8381,7 +8379,7 @@
         <v>-0.086369574069976807</v>
       </c>
       <c r="C920" s="1">
-        <v>0.34085240960121155</v>
+        <v>0.33282181620597839</v>
       </c>
     </row>
     <row r="921">
@@ -8392,7 +8390,7 @@
         <v>-0.20275706052780151</v>
       </c>
       <c r="C921" s="1">
-        <v>0.22351852059364319</v>
+        <v>0.016274049878120422</v>
       </c>
     </row>
     <row r="922">
@@ -8403,7 +8401,7 @@
         <v>-0.050333276391029358</v>
       </c>
       <c r="C922" s="1">
-        <v>-0.49069353938102722</v>
+        <v>-0.44484683871269226</v>
       </c>
     </row>
     <row r="923">
@@ -8414,7 +8412,7 @@
         <v>-0.14091098308563232</v>
       </c>
       <c r="C923" s="1">
-        <v>0.31179553270339966</v>
+        <v>0.40447881817817688</v>
       </c>
     </row>
     <row r="924">
@@ -8425,7 +8423,7 @@
         <v>-0.48422974348068237</v>
       </c>
       <c r="C924" s="1">
-        <v>0.198133185505867</v>
+        <v>-0.084417060017585754</v>
       </c>
     </row>
     <row r="925">
@@ -8436,7 +8434,7 @@
         <v>-0.24804592132568359</v>
       </c>
       <c r="C925" s="1">
-        <v>-0.22924250364303589</v>
+        <v>-0.303301602602005</v>
       </c>
     </row>
     <row r="926">
@@ -8447,7 +8445,7 @@
         <v>-0.39754787087440491</v>
       </c>
       <c r="C926" s="1">
-        <v>-0.038281843066215515</v>
+        <v>0.06509736180305481</v>
       </c>
     </row>
     <row r="927">
@@ -8458,7 +8456,7 @@
         <v>0.09089004248380661</v>
       </c>
       <c r="C927" s="1">
-        <v>-0.26202186942100525</v>
+        <v>-0.40457987785339355</v>
       </c>
     </row>
     <row r="928">
@@ -8469,7 +8467,7 @@
         <v>0.43956553936004639</v>
       </c>
       <c r="C928" s="1">
-        <v>-0.48018765449523926</v>
+        <v>-0.97694087028503418</v>
       </c>
     </row>
     <row r="929">
@@ -8480,7 +8478,7 @@
         <v>-0.1545463502407074</v>
       </c>
       <c r="C929" s="1">
-        <v>-0.12172812968492508</v>
+        <v>-0.20858179032802582</v>
       </c>
     </row>
     <row r="930">
@@ -8491,7 +8489,7 @@
         <v>-0.28456917405128479</v>
       </c>
       <c r="C930" s="1">
-        <v>0.16978085041046143</v>
+        <v>0.13514547049999237</v>
       </c>
     </row>
     <row r="931">
@@ -8502,7 +8500,7 @@
         <v>-0.48715156316757202</v>
       </c>
       <c r="C931" s="1">
-        <v>-0.016661068424582481</v>
+        <v>-0.13812907040119171</v>
       </c>
     </row>
     <row r="932">
@@ -8513,7 +8511,7 @@
         <v>0.056314680725336075</v>
       </c>
       <c r="C932" s="1">
-        <v>-0.096024110913276672</v>
+        <v>-0.14283452928066254</v>
       </c>
     </row>
     <row r="933">
@@ -8524,7 +8522,7 @@
         <v>-0.27726453542709351</v>
       </c>
       <c r="C933" s="1">
-        <v>0.10498779267072678</v>
+        <v>0.068525135517120361</v>
       </c>
     </row>
     <row r="934">
@@ -8535,7 +8533,7 @@
         <v>-0.074682123959064484</v>
       </c>
       <c r="C934" s="1">
-        <v>-0.23479115962982178</v>
+        <v>-0.17729701101779938</v>
       </c>
     </row>
     <row r="935">
@@ -8546,7 +8544,7 @@
         <v>-0.42530554533004761</v>
       </c>
       <c r="C935" s="1">
-        <v>-0.39760693907737732</v>
+        <v>-0.53794550895690918</v>
       </c>
     </row>
     <row r="936">
@@ -8557,7 +8555,7 @@
         <v>-0.8372880220413208</v>
       </c>
       <c r="C936" s="1">
-        <v>-0.10222438722848892</v>
+        <v>-0.28223150968551636</v>
       </c>
     </row>
     <row r="937">
@@ -8568,7 +8566,7 @@
         <v>-0.20373101532459259</v>
       </c>
       <c r="C937" s="1">
-        <v>-0.46736130118370056</v>
+        <v>-0.55216169357299805</v>
       </c>
     </row>
     <row r="938">
@@ -8579,7 +8577,7 @@
         <v>0.019791401922702789</v>
       </c>
       <c r="C938" s="1">
-        <v>-0.31062063574790955</v>
+        <v>-0.24529556930065155</v>
       </c>
     </row>
     <row r="939">
@@ -8590,7 +8588,7 @@
         <v>-0.18230403959751129</v>
       </c>
       <c r="C939" s="1">
-        <v>-0.027133921161293983</v>
+        <v>0.095017194747924805</v>
       </c>
     </row>
     <row r="940">
@@ -8601,7 +8599,7 @@
         <v>-0.2290538102388382</v>
       </c>
       <c r="C940" s="1">
-        <v>-0.20416389405727386</v>
+        <v>-0.69697415828704834</v>
       </c>
     </row>
     <row r="941">
@@ -8609,10 +8607,10 @@
         <v>199102</v>
       </c>
       <c r="B941" s="1">
-        <v>0.58468466997146606</v>
+        <v>0.58468466997146607</v>
       </c>
       <c r="C941" s="1">
-        <v>-0.34028291702270508</v>
+        <v>-0.44554176926612854</v>
       </c>
     </row>
     <row r="942">
@@ -8623,7 +8621,7 @@
         <v>0.69815027713775635</v>
       </c>
       <c r="C942" s="1">
-        <v>0.21176452934741974</v>
+        <v>0.27628928422927856</v>
       </c>
     </row>
     <row r="943">
@@ -8634,7 +8632,7 @@
         <v>-0.24999383091926575</v>
       </c>
       <c r="C943" s="1">
-        <v>0.11432003229856491</v>
+        <v>0.069508381187915802</v>
       </c>
     </row>
     <row r="944">
@@ -8645,7 +8643,7 @@
         <v>-0.1014658585190773</v>
       </c>
       <c r="C944" s="1">
-        <v>-0.16614927351474762</v>
+        <v>-0.25389936566352844</v>
       </c>
     </row>
     <row r="945">
@@ -8656,7 +8654,7 @@
         <v>-0.48374274373054504</v>
       </c>
       <c r="C945" s="1">
-        <v>0.32119765877723694</v>
+        <v>0.4662114679813385</v>
       </c>
     </row>
     <row r="946">
@@ -8667,7 +8665,7 @@
         <v>0.2184780091047287</v>
       </c>
       <c r="C946" s="1">
-        <v>-0.29674366116523743</v>
+        <v>-0.18474648892879486</v>
       </c>
     </row>
     <row r="947">
@@ -8678,7 +8676,7 @@
         <v>-0.25048080086708069</v>
       </c>
       <c r="C947" s="1">
-        <v>-0.31649899482727051</v>
+        <v>-0.25127139687538147</v>
       </c>
     </row>
     <row r="948">
@@ -8689,7 +8687,7 @@
         <v>-0.66148936748504639</v>
       </c>
       <c r="C948" s="1">
-        <v>-0.34248536825180054</v>
+        <v>-0.41732010245323181</v>
       </c>
     </row>
     <row r="949">
@@ -8700,7 +8698,7 @@
         <v>-0.069325380027294159</v>
       </c>
       <c r="C949" s="1">
-        <v>-0.13284845650196075</v>
+        <v>-0.15467356145381927</v>
       </c>
     </row>
     <row r="950">
@@ -8711,7 +8709,7 @@
         <v>0.011512799188494682</v>
       </c>
       <c r="C950" s="1">
-        <v>-0.034337874501943588</v>
+        <v>0.01150037907063961</v>
       </c>
     </row>
     <row r="951">
@@ -8722,7 +8720,7 @@
         <v>-0.42287066578865051</v>
       </c>
       <c r="C951" s="1">
-        <v>-0.03114062175154686</v>
+        <v>-0.14079678058624268</v>
       </c>
     </row>
     <row r="952">
@@ -8733,7 +8731,7 @@
         <v>0.74684804677963257</v>
       </c>
       <c r="C952" s="1">
-        <v>-0.12590649724006653</v>
+        <v>-0.20931629836559296</v>
       </c>
     </row>
     <row r="953">
@@ -8744,7 +8742,7 @@
         <v>0.018817448988556862</v>
       </c>
       <c r="C953" s="1">
-        <v>0.083466552197933197</v>
+        <v>0.086389653384685516</v>
       </c>
     </row>
     <row r="954">
@@ -8755,7 +8753,7 @@
         <v>-0.51052647829055786</v>
       </c>
       <c r="C954" s="1">
-        <v>0.18315242230892181</v>
+        <v>0.1715293675661087</v>
       </c>
     </row>
     <row r="955">
@@ -8766,7 +8764,7 @@
         <v>-0.044002577662467957</v>
       </c>
       <c r="C955" s="1">
-        <v>-0.19103057682514191</v>
+        <v>-0.28342357277870178</v>
       </c>
     </row>
     <row r="956">
@@ -8777,7 +8775,7 @@
         <v>0.034887693822383881</v>
       </c>
       <c r="C956" s="1">
-        <v>-0.33090916275978088</v>
+        <v>-0.30342027544975281</v>
       </c>
     </row>
     <row r="957">
@@ -8788,7 +8786,7 @@
         <v>-0.52270090579986572</v>
       </c>
       <c r="C957" s="1">
-        <v>-0.34523209929466248</v>
+        <v>-0.44617843627929688</v>
       </c>
     </row>
     <row r="958">
@@ -8799,7 +8797,7 @@
         <v>-0.52805763483047485</v>
       </c>
       <c r="C958" s="1">
-        <v>-0.46736478805541992</v>
+        <v>-0.35197919607162476</v>
       </c>
     </row>
     <row r="959">
@@ -8810,7 +8808,7 @@
         <v>-0.85871505737304688</v>
       </c>
       <c r="C959" s="1">
-        <v>-0.27983355522155762</v>
+        <v>-0.1807122528553009</v>
       </c>
     </row>
     <row r="960">
@@ -8821,7 +8819,7 @@
         <v>0.35044878721237183</v>
       </c>
       <c r="C960" s="1">
-        <v>0.77889806032180786</v>
+        <v>0.76660376787185669</v>
       </c>
     </row>
     <row r="961">
@@ -8832,7 +8830,7 @@
         <v>1.2742440700531006</v>
       </c>
       <c r="C961" s="1">
-        <v>0.28638678789138794</v>
+        <v>0.32433515787124634</v>
       </c>
     </row>
     <row r="962">
@@ -8840,10 +8838,10 @@
         <v>199211</v>
       </c>
       <c r="B962" s="1">
-        <v>0.5510832667350769</v>
+        <v>0.55108326673507691</v>
       </c>
       <c r="C962" s="1">
-        <v>0.45630407333374023</v>
+        <v>0.5836174488067627</v>
       </c>
     </row>
     <row r="963">
@@ -8854,7 +8852,7 @@
         <v>-0.19106961786746979</v>
       </c>
       <c r="C963" s="1">
-        <v>0.062879063189029694</v>
+        <v>0.26259496808052063</v>
       </c>
     </row>
     <row r="964">
@@ -8865,7 +8863,7 @@
         <v>0.13910076022148132</v>
       </c>
       <c r="C964" s="1">
-        <v>0.38740026950836182</v>
+        <v>0.16129001975059509</v>
       </c>
     </row>
     <row r="965">
@@ -8876,7 +8874,7 @@
         <v>0.29249852895736694</v>
       </c>
       <c r="C965" s="1">
-        <v>0.47744208574295044</v>
+        <v>0.52339297533035278</v>
       </c>
     </row>
     <row r="966">
@@ -8887,7 +8885,7 @@
         <v>0.21166032552719116</v>
       </c>
       <c r="C966" s="1">
-        <v>0.010789510793983936</v>
+        <v>0.059672340750694275</v>
       </c>
     </row>
     <row r="967">
@@ -8898,7 +8896,7 @@
         <v>0.72055119276046753</v>
       </c>
       <c r="C967" s="1">
-        <v>-0.70240455865859985</v>
+        <v>-0.82197952270507813</v>
       </c>
     </row>
     <row r="968">
@@ -8909,7 +8907,7 @@
         <v>0.038783501833677292</v>
       </c>
       <c r="C968" s="1">
-        <v>-0.25132223963737488</v>
+        <v>-0.20892918109893799</v>
       </c>
     </row>
     <row r="969">
@@ -8920,7 +8918,7 @@
         <v>-0.23538452386856079</v>
       </c>
       <c r="C969" s="1">
-        <v>-0.020871011540293694</v>
+        <v>0.11249102652072906</v>
       </c>
     </row>
     <row r="970">
@@ -8931,7 +8929,7 @@
         <v>0.25451427698135376</v>
       </c>
       <c r="C970" s="1">
-        <v>0.20205122232437134</v>
+        <v>0.4192865788936615</v>
       </c>
     </row>
     <row r="971">
@@ -8942,7 +8940,7 @@
         <v>0.49654185771942139</v>
       </c>
       <c r="C971" s="1">
-        <v>-0.039367213845252991</v>
+        <v>0.10572622716426849</v>
       </c>
     </row>
     <row r="972">
@@ -8953,7 +8951,7 @@
         <v>-0.099517948925495148</v>
       </c>
       <c r="C972" s="1">
-        <v>-0.14207933843135834</v>
+        <v>-0.1485481858253479</v>
       </c>
     </row>
     <row r="973">
@@ -8964,7 +8962,7 @@
         <v>0.44589623808860779</v>
       </c>
       <c r="C973" s="1">
-        <v>-0.16477182507514954</v>
+        <v>-0.13582418859004974</v>
       </c>
     </row>
     <row r="974">
@@ -8975,7 +8973,7 @@
         <v>-0.26022034883499146</v>
       </c>
       <c r="C974" s="1">
-        <v>0.054014291614294052</v>
+        <v>0.20082332193851471</v>
       </c>
     </row>
     <row r="975">
@@ -8986,7 +8984,7 @@
         <v>0.27740222215652466</v>
       </c>
       <c r="C975" s="1">
-        <v>-0.1225079745054245</v>
+        <v>-0.017743827775120735</v>
       </c>
     </row>
     <row r="976">
@@ -8997,7 +8995,7 @@
         <v>0.87102711200714111</v>
       </c>
       <c r="C976" s="1">
-        <v>-0.22409538924694061</v>
+        <v>-0.048435486853122711</v>
       </c>
     </row>
     <row r="977">
@@ -9008,7 +9006,7 @@
         <v>-0.098057016730308533</v>
       </c>
       <c r="C977" s="1">
-        <v>-0.0213339664041996</v>
+        <v>-0.073583707213401794</v>
       </c>
     </row>
     <row r="978">
@@ -9019,7 +9017,7 @@
         <v>-0.34885013103485107</v>
       </c>
       <c r="C978" s="1">
-        <v>-0.11290600895881653</v>
+        <v>-0.11907976865768433</v>
       </c>
     </row>
     <row r="979">
@@ -9030,7 +9028,7 @@
         <v>0.23162639141082764</v>
       </c>
       <c r="C979" s="1">
-        <v>-0.17250643670558929</v>
+        <v>-0.17595759034156799</v>
       </c>
     </row>
     <row r="980">
@@ -9041,7 +9039,7 @@
         <v>-0.23441058397293091</v>
       </c>
       <c r="C980" s="1">
-        <v>-0.15747006237506866</v>
+        <v>-0.094512827694416046</v>
       </c>
     </row>
     <row r="981">
@@ -9052,7 +9050,7 @@
         <v>-0.25973337888717651</v>
       </c>
       <c r="C981" s="1">
-        <v>0.0098581789061427116</v>
+        <v>-0.26173847913742065</v>
       </c>
     </row>
     <row r="982">
@@ -9063,7 +9061,7 @@
         <v>0.40450319647789001</v>
       </c>
       <c r="C982" s="1">
-        <v>-0.3836199939250946</v>
+        <v>-0.35221773386001587</v>
       </c>
     </row>
     <row r="983">
@@ -9074,7 +9072,7 @@
         <v>0.26035800576210022</v>
       </c>
       <c r="C983" s="1">
-        <v>-0.074480034410953522</v>
+        <v>-0.043726969510316849</v>
       </c>
     </row>
     <row r="984">
@@ -9085,7 +9083,7 @@
         <v>-0.22028824687004089</v>
       </c>
       <c r="C984" s="1">
-        <v>-0.26449072360992432</v>
+        <v>-0.30299761891365051</v>
       </c>
     </row>
     <row r="985">
@@ -9096,7 +9094,7 @@
         <v>0.18098077178001404</v>
       </c>
       <c r="C985" s="1">
-        <v>-0.47274979948997498</v>
+        <v>-0.47369158267974854</v>
       </c>
     </row>
     <row r="986">
@@ -9107,7 +9105,7 @@
         <v>-0.32693618535995483</v>
       </c>
       <c r="C986" s="1">
-        <v>0.10867366939783096</v>
+        <v>0.31601321697235108</v>
       </c>
     </row>
     <row r="987">
@@ -9118,7 +9116,7 @@
         <v>-0.011862096376717091</v>
       </c>
       <c r="C987" s="1">
-        <v>0.21735671162605286</v>
+        <v>0.38633665442466736</v>
       </c>
     </row>
     <row r="988">
@@ -9129,7 +9127,7 @@
         <v>-0.12386680394411087</v>
       </c>
       <c r="C988" s="1">
-        <v>-0.24432122707366943</v>
+        <v>-0.17882627248764038</v>
       </c>
     </row>
     <row r="989">
@@ -9140,7 +9138,7 @@
         <v>-0.25048080086708069</v>
       </c>
       <c r="C989" s="1">
-        <v>-0.097479738295078278</v>
+        <v>-0.12107077240943909</v>
       </c>
     </row>
     <row r="990">
@@ -9151,7 +9149,7 @@
         <v>-0.39462599158287048</v>
       </c>
       <c r="C990" s="1">
-        <v>-0.39970782399177551</v>
+        <v>-0.35400488972663879</v>
       </c>
     </row>
     <row r="991">
@@ -9162,7 +9160,7 @@
         <v>0.54816138744354248</v>
       </c>
       <c r="C991" s="1">
-        <v>0.7643926739692688</v>
+        <v>-0.19015461206436157</v>
       </c>
     </row>
     <row r="992">
@@ -9173,7 +9171,7 @@
         <v>0.16442355513572693</v>
       </c>
       <c r="C992" s="1">
-        <v>0.097985565662384033</v>
+        <v>0.15325938165187836</v>
       </c>
     </row>
     <row r="993">
@@ -9181,10 +9179,10 @@
         <v>199506</v>
       </c>
       <c r="B993" s="1">
-        <v>0.48339346051216125</v>
+        <v>0.48339346051216126</v>
       </c>
       <c r="C993" s="1">
-        <v>-0.13905708491802216</v>
+        <v>-0.17864194512367249</v>
       </c>
     </row>
     <row r="994">
@@ -9195,7 +9193,7 @@
         <v>0.36651900410652161</v>
       </c>
       <c r="C994" s="1">
-        <v>-0.19906263053417206</v>
+        <v>-0.11624697595834732</v>
       </c>
     </row>
     <row r="995">
@@ -9206,7 +9204,7 @@
         <v>0.061184439808130264</v>
       </c>
       <c r="C995" s="1">
-        <v>0.068592891097068787</v>
+        <v>0.26191747188568115</v>
       </c>
     </row>
     <row r="996">
@@ -9217,7 +9215,7 @@
         <v>-0.0016355792758986354</v>
       </c>
       <c r="C996" s="1">
-        <v>0.15431943535804749</v>
+        <v>0.26257389783859253</v>
       </c>
     </row>
     <row r="997">
@@ -9228,7 +9226,7 @@
         <v>-0.73161405324935913</v>
       </c>
       <c r="C997" s="1">
-        <v>-0.14749328792095184</v>
+        <v>-0.058671005070209503</v>
       </c>
     </row>
     <row r="998">
@@ -9239,7 +9237,7 @@
         <v>-0.099517948925495148</v>
       </c>
       <c r="C998" s="1">
-        <v>-0.08758246898651123</v>
+        <v>0.093836598098278046</v>
       </c>
     </row>
     <row r="999">
@@ -9250,7 +9248,7 @@
         <v>-0.69119495153427124</v>
       </c>
       <c r="C999" s="1">
-        <v>0.180262491106987</v>
+        <v>0.31916683912277222</v>
       </c>
     </row>
     <row r="1000">
@@ -9261,7 +9259,7 @@
         <v>0.093324922025203705</v>
       </c>
       <c r="C1000" s="1">
-        <v>0.19532941281795502</v>
+        <v>0.18317326903343201</v>
       </c>
     </row>
     <row r="1001">
@@ -9272,7 +9270,7 @@
         <v>-0.014296981506049633</v>
       </c>
       <c r="C1001" s="1">
-        <v>0.17087371647357941</v>
+        <v>0.13819098472595215</v>
       </c>
     </row>
     <row r="1002">
@@ -9283,7 +9281,7 @@
         <v>0.043653272092342377</v>
       </c>
       <c r="C1002" s="1">
-        <v>0.31419363617897034</v>
+        <v>0.42879393696784973</v>
       </c>
     </row>
     <row r="1003">
@@ -9294,7 +9292,7 @@
         <v>0.2335742861032486</v>
       </c>
       <c r="C1003" s="1">
-        <v>0.16173182427883148</v>
+        <v>0.22413498163223267</v>
       </c>
     </row>
     <row r="1004">
@@ -9305,7 +9303,7 @@
         <v>0.27691525220870972</v>
       </c>
       <c r="C1004" s="1">
-        <v>-0.11861253529787064</v>
+        <v>-0.114625483751297</v>
       </c>
     </row>
     <row r="1005">
@@ -9316,7 +9314,7 @@
         <v>-0.28456917405128479</v>
       </c>
       <c r="C1005" s="1">
-        <v>-0.21783499419689178</v>
+        <v>-0.13081768155097962</v>
       </c>
     </row>
     <row r="1006">
@@ -9327,7 +9325,7 @@
         <v>-0.17012961208820343</v>
       </c>
       <c r="C1006" s="1">
-        <v>-0.12333787977695465</v>
+        <v>-0.086523823440074921</v>
       </c>
     </row>
     <row r="1007">
@@ -9338,7 +9336,7 @@
         <v>0.42641717195510864</v>
       </c>
       <c r="C1007" s="1">
-        <v>-0.33435964584350586</v>
+        <v>-0.18041132390499115</v>
       </c>
     </row>
     <row r="1008">
@@ -9349,7 +9347,7 @@
         <v>0.070437006652355194</v>
       </c>
       <c r="C1008" s="1">
-        <v>0.05927034467458725</v>
+        <v>0.1112746000289917</v>
       </c>
     </row>
     <row r="1009">
@@ -9360,7 +9358,7 @@
         <v>0.0037211626768112183</v>
       </c>
       <c r="C1009" s="1">
-        <v>0.065499559044837952</v>
+        <v>0.11521797627210617</v>
       </c>
     </row>
     <row r="1010">
@@ -9371,7 +9369,7 @@
         <v>0.43518275022506714</v>
       </c>
       <c r="C1010" s="1">
-        <v>-0.059269983321428299</v>
+        <v>0.14209343492984772</v>
       </c>
     </row>
     <row r="1011">
@@ -9382,7 +9380,7 @@
         <v>0.14494447410106659</v>
       </c>
       <c r="C1011" s="1">
-        <v>0.33130654692649841</v>
+        <v>0.44570848345756531</v>
       </c>
     </row>
     <row r="1012">
@@ -9393,7 +9391,7 @@
         <v>0.51894277334213257</v>
       </c>
       <c r="C1012" s="1">
-        <v>0.12966130673885345</v>
+        <v>0.22473172843456268</v>
       </c>
     </row>
     <row r="1013">
@@ -9404,7 +9402,7 @@
         <v>0.10988213866949081</v>
       </c>
       <c r="C1013" s="1">
-        <v>0.34481856226921082</v>
+        <v>0.4672149121761322</v>
       </c>
     </row>
     <row r="1014">
@@ -9415,7 +9413,7 @@
         <v>-0.12484075129032135</v>
       </c>
       <c r="C1014" s="1">
-        <v>0.14823822677135468</v>
+        <v>0.16273821890354157</v>
       </c>
     </row>
     <row r="1015">
@@ -9426,7 +9424,7 @@
         <v>0.12546540796756744</v>
       </c>
       <c r="C1015" s="1">
-        <v>0.037417963147163391</v>
+        <v>-0.057161234319210053</v>
       </c>
     </row>
     <row r="1016">
@@ -9437,7 +9435,7 @@
         <v>0.1147519126534462</v>
       </c>
       <c r="C1016" s="1">
-        <v>0.056562617421150208</v>
+        <v>0.073744580149650574</v>
       </c>
     </row>
     <row r="1017">
@@ -9448,7 +9446,7 @@
         <v>0.28227198123931885</v>
       </c>
       <c r="C1017" s="1">
-        <v>-4.9817231229098979e-06</v>
+        <v>0.04607115313410759</v>
       </c>
     </row>
     <row r="1018">
@@ -9459,7 +9457,7 @@
         <v>0.63435637950897217</v>
       </c>
       <c r="C1018" s="1">
-        <v>0.1791326105594635</v>
+        <v>0.25736847519874573</v>
       </c>
     </row>
     <row r="1019">
@@ -9467,10 +9465,10 @@
         <v>199708</v>
       </c>
       <c r="B1019" s="1">
-        <v>-0.48471671342849731</v>
+        <v>-0.48471671342849732</v>
       </c>
       <c r="C1019" s="1">
-        <v>0.39533209800720215</v>
+        <v>0.47042927145957947</v>
       </c>
     </row>
     <row r="1020">
@@ -9481,7 +9479,7 @@
         <v>0.63192141056060791</v>
       </c>
       <c r="C1020" s="1">
-        <v>-0.29332384467124939</v>
+        <v>-0.26359999179840088</v>
       </c>
     </row>
     <row r="1021">
@@ -9492,7 +9490,7 @@
         <v>-0.49786511063575745</v>
       </c>
       <c r="C1021" s="1">
-        <v>-0.11213386803865433</v>
+        <v>-0.1319366991519928</v>
       </c>
     </row>
     <row r="1022">
@@ -9503,7 +9501,7 @@
         <v>-0.14480680227279663</v>
       </c>
       <c r="C1022" s="1">
-        <v>-0.091293118894100189</v>
+        <v>0.0014410271542146802</v>
       </c>
     </row>
     <row r="1023">
@@ -9514,7 +9512,7 @@
         <v>-0.22759288549423218</v>
       </c>
       <c r="C1023" s="1">
-        <v>0.23659896850585938</v>
+        <v>0.34388294816017151</v>
       </c>
     </row>
     <row r="1024">
@@ -9525,7 +9523,7 @@
         <v>0.36359712481498718</v>
       </c>
       <c r="C1024" s="1">
-        <v>0.18962468206882477</v>
+        <v>0.27662307024002075</v>
       </c>
     </row>
     <row r="1025">
@@ -9536,7 +9534,7 @@
         <v>0.76291829347610474</v>
       </c>
       <c r="C1025" s="1">
-        <v>-0.097771205008029938</v>
+        <v>0.0017558214021846652</v>
       </c>
     </row>
     <row r="1026">
@@ -9547,7 +9545,7 @@
         <v>0.27691525220870972</v>
       </c>
       <c r="C1026" s="1">
-        <v>-0.011573754251003265</v>
+        <v>0.0052319010719656944</v>
       </c>
     </row>
     <row r="1027">
@@ -9558,7 +9556,7 @@
         <v>0.58078885078430176</v>
       </c>
       <c r="C1027" s="1">
-        <v>-0.14348451793193817</v>
+        <v>-0.22624528408050537</v>
       </c>
     </row>
     <row r="1028">
@@ -9569,7 +9567,7 @@
         <v>-0.12143190950155258</v>
       </c>
       <c r="C1028" s="1">
-        <v>-0.18479785323143005</v>
+        <v>-0.10114800930023193</v>
       </c>
     </row>
     <row r="1029">
@@ -9580,7 +9578,7 @@
         <v>0.25305336713790894</v>
       </c>
       <c r="C1029" s="1">
-        <v>0.084538981318473816</v>
+        <v>0.11976533383131027</v>
       </c>
     </row>
     <row r="1030">
@@ -9591,7 +9589,7 @@
         <v>0.32317805290222168</v>
       </c>
       <c r="C1030" s="1">
-        <v>0.023417413234710693</v>
+        <v>0.21588407456874848</v>
       </c>
     </row>
     <row r="1031">
@@ -9599,10 +9597,10 @@
         <v>199808</v>
       </c>
       <c r="B1031" s="1">
-        <v>-1.0111387968063354</v>
+        <v>-1.0111387968063355</v>
       </c>
       <c r="C1031" s="1">
-        <v>0.056580882519483566</v>
+        <v>0.083360865712165833</v>
       </c>
     </row>
     <row r="1032">
@@ -9613,7 +9611,7 @@
         <v>-0.17694728076457977</v>
       </c>
       <c r="C1032" s="1">
-        <v>-0.30454474687576294</v>
+        <v>-0.36634773015975952</v>
       </c>
     </row>
     <row r="1033">
@@ -9624,7 +9622,7 @@
         <v>0.44833114743232727</v>
       </c>
       <c r="C1033" s="1">
-        <v>-0.36958888173103333</v>
+        <v>-0.32578125596046448</v>
       </c>
     </row>
     <row r="1034">
@@ -9635,7 +9633,7 @@
         <v>0.4195995032787323</v>
       </c>
       <c r="C1034" s="1">
-        <v>0.18024693429470062</v>
+        <v>0.39672443270683289</v>
       </c>
     </row>
     <row r="1035">
@@ -9646,7 +9644,7 @@
         <v>0.74976986646652222</v>
       </c>
       <c r="C1035" s="1">
-        <v>-0.14712591469287872</v>
+        <v>-0.0380755215883255</v>
       </c>
     </row>
     <row r="1036">
@@ -9657,7 +9655,7 @@
         <v>0.51845580339431763</v>
       </c>
       <c r="C1036" s="1">
-        <v>0.001684746122919023</v>
+        <v>0.18045385181903839</v>
       </c>
     </row>
     <row r="1037">
@@ -9668,7 +9666,7 @@
         <v>-0.15211145579814911</v>
       </c>
       <c r="C1037" s="1">
-        <v>0.302112877368927</v>
+        <v>0.34239906072616577</v>
       </c>
     </row>
     <row r="1038">
@@ -9679,7 +9677,7 @@
         <v>0.5710492730140686</v>
       </c>
       <c r="C1038" s="1">
-        <v>0.17367328703403473</v>
+        <v>0.21091879904270172</v>
       </c>
     </row>
     <row r="1039">
@@ -9690,7 +9688,7 @@
         <v>0.13130912184715271</v>
       </c>
       <c r="C1039" s="1">
-        <v>0.11554828286170959</v>
+        <v>-0.042294174432754517</v>
       </c>
     </row>
     <row r="1040">
@@ -9701,7 +9699,7 @@
         <v>-0.23100173473358154</v>
       </c>
       <c r="C1040" s="1">
-        <v>0.086266010999679565</v>
+        <v>0.094416618347167969</v>
       </c>
     </row>
     <row r="1041">
@@ -9712,7 +9710,7 @@
         <v>0.63533025979995728</v>
       </c>
       <c r="C1041" s="1">
-        <v>0.10276263952255249</v>
+        <v>0.24180379509925842</v>
       </c>
     </row>
     <row r="1042">
@@ -9723,7 +9721,7 @@
         <v>-0.087830498814582825</v>
       </c>
       <c r="C1042" s="1">
-        <v>0.044105183333158493</v>
+        <v>0.20365768671035767</v>
       </c>
     </row>
     <row r="1043">
@@ -9734,7 +9732,7 @@
         <v>-0.088317476212978363</v>
       </c>
       <c r="C1043" s="1">
-        <v>-0.15847083926200867</v>
+        <v>-0.11272554844617844</v>
       </c>
     </row>
     <row r="1044">
@@ -9745,7 +9743,7 @@
         <v>0.15663193166255951</v>
       </c>
       <c r="C1044" s="1">
-        <v>0.010968334972858429</v>
+        <v>-0.01705801859498024</v>
       </c>
     </row>
     <row r="1045">
@@ -9753,10 +9751,10 @@
         <v>199910</v>
       </c>
       <c r="B1045" s="1">
-        <v>0.76584011316299438</v>
+        <v>0.76584011316299439</v>
       </c>
       <c r="C1045" s="1">
-        <v>-0.25529381632804871</v>
+        <v>-0.2570061981678009</v>
       </c>
     </row>
     <row r="1046">
@@ -9767,7 +9765,7 @@
         <v>1.1602914333343506</v>
       </c>
       <c r="C1046" s="1">
-        <v>0.16518151760101318</v>
+        <v>0.30597919225692749</v>
       </c>
     </row>
     <row r="1047">
@@ -9778,7 +9776,7 @@
         <v>1.4456599950790405</v>
       </c>
       <c r="C1047" s="1">
-        <v>-0.12914882600307465</v>
+        <v>-0.17512118816375732</v>
       </c>
     </row>
     <row r="1048">
@@ -9789,7 +9787,7 @@
         <v>0.048036068677902222</v>
       </c>
       <c r="C1048" s="1">
-        <v>0.0056281718425452709</v>
+        <v>0.095420956611633301</v>
       </c>
     </row>
     <row r="1049">
@@ -9800,7 +9798,7 @@
         <v>0.38161525130271912</v>
       </c>
       <c r="C1049" s="1">
-        <v>0.15583376586437225</v>
+        <v>0.0058942935429513455</v>
       </c>
     </row>
     <row r="1050">
@@ -9811,7 +9809,7 @@
         <v>0.10209051519632339</v>
       </c>
       <c r="C1050" s="1">
-        <v>0.13954704999923706</v>
+        <v>0.03529265895485878</v>
       </c>
     </row>
     <row r="1051">
@@ -9822,7 +9820,7 @@
         <v>0.30467292666435242</v>
       </c>
       <c r="C1051" s="1">
-        <v>0.14392790198326111</v>
+        <v>0.17095942795276642</v>
       </c>
     </row>
     <row r="1052">
@@ -9833,7 +9831,7 @@
         <v>-0.56798982620239258</v>
       </c>
       <c r="C1052" s="1">
-        <v>0.35793858766555786</v>
+        <v>0.37194737792015076</v>
       </c>
     </row>
     <row r="1053">
@@ -9844,7 +9842,7 @@
         <v>-0.27190777659416199</v>
       </c>
       <c r="C1053" s="1">
-        <v>-0.2281576544046402</v>
+        <v>-0.25612321496009827</v>
       </c>
     </row>
     <row r="1054">
@@ -9855,7 +9853,7 @@
         <v>-0.4793599545955658</v>
       </c>
       <c r="C1054" s="1">
-        <v>0.059306781738996506</v>
+        <v>0.26389190554618835</v>
       </c>
     </row>
     <row r="1055">
@@ -9863,10 +9861,10 @@
         <v>200008</v>
       </c>
       <c r="B1055" s="1">
-        <v>0.026609081774950027</v>
+        <v>0.026609081774950028</v>
       </c>
       <c r="C1055" s="1">
-        <v>0.2799479067325592</v>
+        <v>0.26368868350982666</v>
       </c>
     </row>
     <row r="1056">
@@ -9877,7 +9875,7 @@
         <v>-0.43309715390205383</v>
       </c>
       <c r="C1056" s="1">
-        <v>0.30150884389877319</v>
+        <v>0.11513469368219376</v>
       </c>
     </row>
     <row r="1057">
@@ -9888,7 +9886,7 @@
         <v>0.15127518773078918</v>
       </c>
       <c r="C1057" s="1">
-        <v>0.1421559751033783</v>
+        <v>0.22265668213367462</v>
       </c>
     </row>
     <row r="1058">
@@ -9899,7 +9897,7 @@
         <v>-0.11266632378101349</v>
       </c>
       <c r="C1058" s="1">
-        <v>-0.0015791988698765635</v>
+        <v>0.099207788705825806</v>
       </c>
     </row>
     <row r="1059">
@@ -9910,7 +9908,7 @@
         <v>-0.077603988349437714</v>
       </c>
       <c r="C1059" s="1">
-        <v>-0.37733522057533264</v>
+        <v>-0.28254327178001404</v>
       </c>
     </row>
     <row r="1060">
@@ -9921,7 +9919,7 @@
         <v>-0.81926995515823364</v>
       </c>
       <c r="C1060" s="1">
-        <v>-0.32106795907020569</v>
+        <v>-0.26219969987869263</v>
       </c>
     </row>
     <row r="1061">
@@ -9932,7 +9930,7 @@
         <v>-1.4265302419662476</v>
       </c>
       <c r="C1061" s="1">
-        <v>0.29939156770706177</v>
+        <v>0.18125848472118378</v>
       </c>
     </row>
     <row r="1062">
@@ -9943,7 +9941,7 @@
         <v>0.14348354935646057</v>
       </c>
       <c r="C1062" s="1">
-        <v>0.18590061366558075</v>
+        <v>0.10557539016008377</v>
       </c>
     </row>
     <row r="1063">
@@ -9954,7 +9952,7 @@
         <v>1.4198501110076904</v>
       </c>
       <c r="C1063" s="1">
-        <v>-0.020203467458486557</v>
+        <v>-0.065555192530155182</v>
       </c>
     </row>
     <row r="1064">
@@ -9965,7 +9963,7 @@
         <v>-0.32791012525558472</v>
       </c>
       <c r="C1064" s="1">
-        <v>0.20640602707862854</v>
+        <v>0.077056951820850372</v>
       </c>
     </row>
     <row r="1065">
@@ -9976,7 +9974,7 @@
         <v>-0.90205597877502441</v>
       </c>
       <c r="C1065" s="1">
-        <v>0.29489558935165405</v>
+        <v>0.41211420297622681</v>
       </c>
     </row>
     <row r="1066">
@@ -9987,7 +9985,7 @@
         <v>-0.33764967322349548</v>
       </c>
       <c r="C1066" s="1">
-        <v>0.040366817265748978</v>
+        <v>0.40616986155509949</v>
       </c>
     </row>
     <row r="1067">
@@ -9998,7 +9996,7 @@
         <v>-1.0963598489761353</v>
       </c>
       <c r="C1067" s="1">
-        <v>-0.38572105765342712</v>
+        <v>-0.48339304327964783</v>
       </c>
     </row>
     <row r="1068">
@@ -10009,7 +10007,7 @@
         <v>-0.13945005834102631</v>
       </c>
       <c r="C1068" s="1">
-        <v>-0.2866281270980835</v>
+        <v>-0.49377301335334778</v>
       </c>
     </row>
     <row r="1069">
@@ -10020,7 +10018,7 @@
         <v>1.1106197834014893</v>
       </c>
       <c r="C1069" s="1">
-        <v>0.09333965927362442</v>
+        <v>0.29970115423202515</v>
       </c>
     </row>
     <row r="1070">
@@ -10028,10 +10026,10 @@
         <v>200111</v>
       </c>
       <c r="B1070" s="1">
-        <v>0.43372184038162231</v>
+        <v>0.43372184038162232</v>
       </c>
       <c r="C1070" s="1">
-        <v>-0.029332669451832771</v>
+        <v>0.23294724524021149</v>
       </c>
     </row>
     <row r="1071">
@@ -10042,7 +10040,7 @@
         <v>0.31295153498649597</v>
       </c>
       <c r="C1071" s="1">
-        <v>0.1217198520898819</v>
+        <v>0.25189569592475891</v>
       </c>
     </row>
     <row r="1072">
@@ -10050,10 +10048,10 @@
         <v>200201</v>
       </c>
       <c r="B1072" s="1">
-        <v>-0.2431761622428894</v>
+        <v>-0.24317616224288941</v>
       </c>
       <c r="C1072" s="1">
-        <v>-0.1172545850276947</v>
+        <v>-0.19811326265335083</v>
       </c>
     </row>
     <row r="1073">
@@ -10064,7 +10062,7 @@
         <v>-0.2456110417842865</v>
       </c>
       <c r="C1073" s="1">
-        <v>0.24989627301692963</v>
+        <v>0.31301489472389221</v>
       </c>
     </row>
     <row r="1074">
@@ -10075,7 +10073,7 @@
         <v>-0.062020722776651382</v>
       </c>
       <c r="C1074" s="1">
-        <v>-0.13158483803272247</v>
+        <v>-0.25733968615531921</v>
       </c>
     </row>
     <row r="1075">
@@ -10086,7 +10084,7 @@
         <v>-0.89182943105697632</v>
       </c>
       <c r="C1075" s="1">
-        <v>-0.085065193474292755</v>
+        <v>-0.1686539500951767</v>
       </c>
     </row>
     <row r="1076">
@@ -10097,7 +10095,7 @@
         <v>-0.41897484660148621</v>
       </c>
       <c r="C1076" s="1">
-        <v>-0.3578355610370636</v>
+        <v>-0.40042170882225037</v>
       </c>
     </row>
     <row r="1077">
@@ -10108,7 +10106,7 @@
         <v>-0.25535058975219727</v>
       </c>
       <c r="C1077" s="1">
-        <v>-0.13025063276290894</v>
+        <v>0.010499882511794567</v>
       </c>
     </row>
     <row r="1078">
@@ -10119,7 +10117,7 @@
         <v>-0.6590544581413269</v>
       </c>
       <c r="C1078" s="1">
-        <v>-0.35244804620742798</v>
+        <v>-0.2496720552444458</v>
       </c>
     </row>
     <row r="1079">
@@ -10130,7 +10128,7 @@
         <v>0.12449145317077637</v>
       </c>
       <c r="C1079" s="1">
-        <v>1.0732933282852173</v>
+        <v>0.15219767391681671</v>
       </c>
     </row>
     <row r="1080">
@@ -10141,7 +10139,7 @@
         <v>-0.31476178765296936</v>
       </c>
       <c r="C1080" s="1">
-        <v>0.046775393187999725</v>
+        <v>0.0054367752745747566</v>
       </c>
     </row>
     <row r="1081">
@@ -10152,7 +10150,7 @@
         <v>0.8773578405380249</v>
       </c>
       <c r="C1081" s="1">
-        <v>-0.2040071040391922</v>
+        <v>-0.21634030342102051</v>
       </c>
     </row>
     <row r="1082">
@@ -10163,7 +10161,7 @@
         <v>0.52332556247711182</v>
       </c>
       <c r="C1082" s="1">
-        <v>-0.13442990183830261</v>
+        <v>0.062398910522460938</v>
       </c>
     </row>
     <row r="1083">
@@ -10174,7 +10172,7 @@
         <v>-0.84361869096755981</v>
       </c>
       <c r="C1083" s="1">
-        <v>-0.075008288025856018</v>
+        <v>-0.00085767114069312811</v>
       </c>
     </row>
     <row r="1084">
@@ -10185,7 +10183,7 @@
         <v>-0.57091164588928223</v>
       </c>
       <c r="C1084" s="1">
-        <v>-0.3383585512638092</v>
+        <v>-0.34689810872077942</v>
       </c>
     </row>
     <row r="1085">
@@ -10196,7 +10194,7 @@
         <v>-0.24512407183647156</v>
       </c>
       <c r="C1085" s="1">
-        <v>-0.0033109919168055058</v>
+        <v>-0.16168323159217834</v>
       </c>
     </row>
     <row r="1086">
@@ -10207,7 +10205,7 @@
         <v>-0.083934687077999115</v>
       </c>
       <c r="C1086" s="1">
-        <v>-0.16717517375946045</v>
+        <v>-0.19292233884334564</v>
       </c>
     </row>
     <row r="1087">
@@ -10218,7 +10216,7 @@
         <v>0.68792378902435303</v>
       </c>
       <c r="C1087" s="1">
-        <v>-0.27463340759277344</v>
+        <v>-0.16271468997001648</v>
       </c>
     </row>
     <row r="1088">
@@ -10229,7 +10227,7 @@
         <v>-0.064455606043338776</v>
       </c>
       <c r="C1088" s="1">
-        <v>-0.36394673585891724</v>
+        <v>-0.27455857396125793</v>
       </c>
     </row>
     <row r="1089">
@@ -10240,7 +10238,7 @@
         <v>-0.14431983232498169</v>
       </c>
       <c r="C1089" s="1">
-        <v>-0.18776550889015198</v>
+        <v>-0.080773264169692993</v>
       </c>
     </row>
     <row r="1090">
@@ -10251,7 +10249,7 @@
         <v>-0.032315131276845932</v>
       </c>
       <c r="C1090" s="1">
-        <v>0.29514914751052856</v>
+        <v>0.61455243825912476</v>
       </c>
     </row>
     <row r="1091">
@@ -10262,7 +10260,7 @@
         <v>0.38015434145927429</v>
       </c>
       <c r="C1091" s="1">
-        <v>0.1981184184551239</v>
+        <v>0.27415347099304199</v>
       </c>
     </row>
     <row r="1092">
@@ -10273,7 +10271,7 @@
         <v>-0.43309715390205383</v>
       </c>
       <c r="C1092" s="1">
-        <v>-0.15656757354736328</v>
+        <v>-0.24162419140338898</v>
       </c>
     </row>
     <row r="1093">
@@ -10284,7 +10282,7 @@
         <v>0.46781021356582642</v>
       </c>
       <c r="C1093" s="1">
-        <v>-0.37912192940711975</v>
+        <v>-0.28969761729240417</v>
       </c>
     </row>
     <row r="1094">
@@ -10295,7 +10293,7 @@
         <v>0.094298884272575378</v>
       </c>
       <c r="C1094" s="1">
-        <v>-0.039664782583713531</v>
+        <v>0.082158774137496948</v>
       </c>
     </row>
     <row r="1095">
@@ -10306,7 +10304,7 @@
         <v>-0.33034500479698181</v>
       </c>
       <c r="C1095" s="1">
-        <v>-0.37730270624160767</v>
+        <v>-0.3706572949886322</v>
       </c>
     </row>
     <row r="1096">
@@ -10317,7 +10315,7 @@
         <v>0.56325769424438477</v>
       </c>
       <c r="C1096" s="1">
-        <v>-0.29125344753265381</v>
+        <v>-0.12602372467517853</v>
       </c>
     </row>
     <row r="1097">
@@ -10328,7 +10326,7 @@
         <v>0.24233987927436829</v>
       </c>
       <c r="C1097" s="1">
-        <v>0.007092619314789772</v>
+        <v>-0.10299196094274521</v>
       </c>
     </row>
     <row r="1098">
@@ -10339,7 +10337,7 @@
         <v>-0.24707198143005371</v>
       </c>
       <c r="C1098" s="1">
-        <v>0.18188130855560303</v>
+        <v>0.41962754726409912</v>
       </c>
     </row>
     <row r="1099">
@@ -10350,7 +10348,7 @@
         <v>-0.84020984172821045</v>
       </c>
       <c r="C1099" s="1">
-        <v>0.031010707840323448</v>
+        <v>0.10639453679323196</v>
       </c>
     </row>
     <row r="1100">
@@ -10358,10 +10356,10 @@
         <v>200405</v>
       </c>
       <c r="B1100" s="1">
-        <v>-0.16964262723922729</v>
+        <v>-0.1696426272392273</v>
       </c>
       <c r="C1100" s="1">
-        <v>-0.059447053819894791</v>
+        <v>-0.032696042209863663</v>
       </c>
     </row>
     <row r="1101">
@@ -10372,7 +10370,7 @@
         <v>0.19802497327327728</v>
       </c>
       <c r="C1101" s="1">
-        <v>0.11640889942646027</v>
+        <v>0.24708610773086548</v>
       </c>
     </row>
     <row r="1102">
@@ -10383,7 +10381,7 @@
         <v>-0.46475064754486084</v>
       </c>
       <c r="C1102" s="1">
-        <v>-0.10491322726011276</v>
+        <v>0.020876424387097359</v>
       </c>
     </row>
     <row r="1103">
@@ -10394,7 +10392,7 @@
         <v>-0.044489555060863495</v>
       </c>
       <c r="C1103" s="1">
-        <v>-0.051261484622955322</v>
+        <v>-0.062552154064178467</v>
       </c>
     </row>
     <row r="1104">
@@ -10405,7 +10403,7 @@
         <v>0.31782132387161255</v>
       </c>
       <c r="C1104" s="1">
-        <v>0.24480310082435608</v>
+        <v>0.22917301952838898</v>
       </c>
     </row>
     <row r="1105">
@@ -10416,7 +10414,7 @@
         <v>0.24428778886795044</v>
       </c>
       <c r="C1105" s="1">
-        <v>-0.43658563494682312</v>
+        <v>-0.51187336444854736</v>
       </c>
     </row>
     <row r="1106">
@@ -10427,7 +10425,7 @@
         <v>0.17465007305145264</v>
       </c>
       <c r="C1106" s="1">
-        <v>-0.36888909339904785</v>
+        <v>-0.15770605206489563</v>
       </c>
     </row>
     <row r="1107">
@@ -10438,7 +10436,7 @@
         <v>-0.1735384464263916</v>
       </c>
       <c r="C1107" s="1">
-        <v>-0.24438638985157013</v>
+        <v>-0.19738085567951202</v>
       </c>
     </row>
     <row r="1108">
@@ -10449,7 +10447,7 @@
         <v>0.0027472104411572218</v>
       </c>
       <c r="C1108" s="1">
-        <v>-0.047802038490772247</v>
+        <v>0.23562599718570709</v>
       </c>
     </row>
     <row r="1109">
@@ -10460,7 +10458,7 @@
         <v>0.23795706033706665</v>
       </c>
       <c r="C1109" s="1">
-        <v>0.14337429404258728</v>
+        <v>0.0011575615499168634</v>
       </c>
     </row>
     <row r="1110">
@@ -10471,7 +10469,7 @@
         <v>-0.10682260245084763</v>
       </c>
       <c r="C1110" s="1">
-        <v>0.19807922840118408</v>
+        <v>0.19905680418014526</v>
       </c>
     </row>
     <row r="1111">
@@ -10482,7 +10480,7 @@
         <v>-0.072247236967086792</v>
       </c>
       <c r="C1111" s="1">
-        <v>-0.25532081723213196</v>
+        <v>-0.23045709729194641</v>
       </c>
     </row>
     <row r="1112">
@@ -10493,7 +10491,7 @@
         <v>0.35434457659721375</v>
       </c>
       <c r="C1112" s="1">
-        <v>0.47469726204872131</v>
+        <v>0.74862509965896606</v>
       </c>
     </row>
     <row r="1113">
@@ -10504,7 +10502,7 @@
         <v>0.12887425720691681</v>
       </c>
       <c r="C1113" s="1">
-        <v>0.29776296019554138</v>
+        <v>0.39970707893371582</v>
       </c>
     </row>
     <row r="1114">
@@ -10515,7 +10513,7 @@
         <v>0.014434655196964741</v>
       </c>
       <c r="C1114" s="1">
-        <v>-0.1292717307806015</v>
+        <v>0.085440404713153839</v>
       </c>
     </row>
     <row r="1115">
@@ -10526,7 +10524,7 @@
         <v>-0.071760259568691254</v>
       </c>
       <c r="C1115" s="1">
-        <v>-0.087303832173347473</v>
+        <v>-0.15659646689891815</v>
       </c>
     </row>
     <row r="1116">
@@ -10537,7 +10535,7 @@
         <v>0.29542034864425659</v>
       </c>
       <c r="C1116" s="1">
-        <v>0.039968274533748627</v>
+        <v>-0.040540602058172226</v>
       </c>
     </row>
     <row r="1117">
@@ -10548,7 +10546,7 @@
         <v>-0.23246265947818756</v>
       </c>
       <c r="C1117" s="1">
-        <v>0.120786152780056</v>
+        <v>0.25722914934158325</v>
       </c>
     </row>
     <row r="1118">
@@ -10556,10 +10554,10 @@
         <v>200511</v>
       </c>
       <c r="B1118" s="1">
-        <v>0.089916087687015533</v>
+        <v>0.089916087687015534</v>
       </c>
       <c r="C1118" s="1">
-        <v>-0.078761115670204163</v>
+        <v>0.084429040551185608</v>
       </c>
     </row>
     <row r="1119">
@@ -10570,7 +10568,7 @@
         <v>0.27058452367782593</v>
       </c>
       <c r="C1119" s="1">
-        <v>0.91491323709487915</v>
+        <v>-0.028116567060351372</v>
       </c>
     </row>
     <row r="1120">
@@ -10581,7 +10579,7 @@
         <v>0.12400446832180023</v>
       </c>
       <c r="C1120" s="1">
-        <v>-0.30747377872467041</v>
+        <v>-0.15171097218990326</v>
       </c>
     </row>
     <row r="1121">
@@ -10592,7 +10590,7 @@
         <v>0.21068637073040009</v>
       </c>
       <c r="C1121" s="1">
-        <v>0.21275271475315094</v>
+        <v>0.046160079538822174</v>
       </c>
     </row>
     <row r="1122">
@@ -10603,7 +10601,7 @@
         <v>0.26035800576210022</v>
       </c>
       <c r="C1122" s="1">
-        <v>0.027689285576343536</v>
+        <v>0.020184725522994995</v>
       </c>
     </row>
     <row r="1123">
@@ -10614,7 +10612,7 @@
         <v>0.016869544982910156</v>
       </c>
       <c r="C1123" s="1">
-        <v>-0.22050030529499054</v>
+        <v>-0.33914464712142944</v>
       </c>
     </row>
     <row r="1124">
@@ -10625,7 +10623,7 @@
         <v>-0.41556599736213684</v>
       </c>
       <c r="C1124" s="1">
-        <v>-0.33085769414901733</v>
+        <v>-0.32325223088264465</v>
       </c>
     </row>
     <row r="1125">
@@ -10636,7 +10634,7 @@
         <v>-0.12532773613929749</v>
       </c>
       <c r="C1125" s="1">
-        <v>0.046728648245334625</v>
+        <v>0.10112950205802917</v>
       </c>
     </row>
     <row r="1126">
@@ -10647,7 +10645,7 @@
         <v>-0.063481658697128296</v>
       </c>
       <c r="C1126" s="1">
-        <v>0.0095533812418580055</v>
+        <v>0.17385144531726837</v>
       </c>
     </row>
     <row r="1127">
@@ -10658,7 +10656,7 @@
         <v>0.14543147385120392</v>
       </c>
       <c r="C1127" s="1">
-        <v>-0.098358489573001862</v>
+        <v>-0.15651415288448334</v>
       </c>
     </row>
     <row r="1128">
@@ -10669,7 +10667,7 @@
         <v>-0.094161204993724823</v>
       </c>
       <c r="C1128" s="1">
-        <v>0.069354161620140076</v>
+        <v>0.1325450986623764</v>
       </c>
     </row>
     <row r="1129">
@@ -10680,7 +10678,7 @@
         <v>0.1274133175611496</v>
       </c>
       <c r="C1129" s="1">
-        <v>0.010951555334031582</v>
+        <v>0.0012558520538732409</v>
       </c>
     </row>
     <row r="1130">
@@ -10691,7 +10689,7 @@
         <v>-0.037671875208616257</v>
       </c>
       <c r="C1130" s="1">
-        <v>0.96551835536956787</v>
+        <v>0.022973231971263885</v>
       </c>
     </row>
     <row r="1131">
@@ -10702,7 +10700,7 @@
         <v>0.12838725745677948</v>
       </c>
       <c r="C1131" s="1">
-        <v>-0.11170364171266556</v>
+        <v>-0.066577397286891937</v>
       </c>
     </row>
     <row r="1132">
@@ -10713,7 +10711,7 @@
         <v>0.17124123871326447</v>
       </c>
       <c r="C1132" s="1">
-        <v>-0.046462047845125198</v>
+        <v>0.11029182374477386</v>
       </c>
     </row>
     <row r="1133">
@@ -10724,7 +10722,7 @@
         <v>-0.096596084535121918</v>
       </c>
       <c r="C1133" s="1">
-        <v>-0.088061362504959106</v>
+        <v>-0.25986644625663757</v>
       </c>
     </row>
     <row r="1134">
@@ -10735,7 +10733,7 @@
         <v>0.20143379271030426</v>
       </c>
       <c r="C1134" s="1">
-        <v>-0.1187288835644722</v>
+        <v>-0.2873927652835846</v>
       </c>
     </row>
     <row r="1135">
@@ -10743,10 +10741,10 @@
         <v>200704</v>
       </c>
       <c r="B1135" s="1">
-        <v>0.22724358737468719</v>
+        <v>0.2272435873746872</v>
       </c>
       <c r="C1135" s="1">
-        <v>0.079491607844829559</v>
+        <v>0.0093643758445978165</v>
       </c>
     </row>
     <row r="1136">
@@ -10757,7 +10755,7 @@
         <v>0.29395943880081177</v>
       </c>
       <c r="C1136" s="1">
-        <v>-0.091209873557090759</v>
+        <v>0.030955342575907707</v>
       </c>
     </row>
     <row r="1137">
@@ -10768,7 +10766,7 @@
         <v>-0.090752363204956055</v>
       </c>
       <c r="C1137" s="1">
-        <v>-0.16318248212337494</v>
+        <v>-0.16635961830615997</v>
       </c>
     </row>
     <row r="1138">
@@ -10779,7 +10777,7 @@
         <v>-0.090752363204956055</v>
       </c>
       <c r="C1138" s="1">
-        <v>-0.13270917534828186</v>
+        <v>-0.024403925985097885</v>
       </c>
     </row>
     <row r="1139">
@@ -10790,7 +10788,7 @@
         <v>0.16880635917186737</v>
       </c>
       <c r="C1139" s="1">
-        <v>0.051814127713441849</v>
+        <v>0.12116021662950516</v>
       </c>
     </row>
     <row r="1140">
@@ -10801,7 +10799,7 @@
         <v>0.24428778886795044</v>
       </c>
       <c r="C1140" s="1">
-        <v>-0.36385631561279297</v>
+        <v>-0.4891008734703064</v>
       </c>
     </row>
     <row r="1141">
@@ -10812,7 +10810,7 @@
         <v>0.04219234362244606</v>
       </c>
       <c r="C1141" s="1">
-        <v>0.0077617978677153587</v>
+        <v>-0.0048494404181838036</v>
       </c>
     </row>
     <row r="1142">
@@ -10823,7 +10821,7 @@
         <v>-0.25973337888717651</v>
       </c>
       <c r="C1142" s="1">
-        <v>-0.40549436211585999</v>
+        <v>-0.48161172866821289</v>
       </c>
     </row>
     <row r="1143">
@@ -10834,7 +10832,7 @@
         <v>-0.17840822041034698</v>
       </c>
       <c r="C1143" s="1">
-        <v>0.19610394537448883</v>
+        <v>0.38464686274528504</v>
       </c>
     </row>
     <row r="1144">
@@ -10845,7 +10843,7 @@
         <v>-0.50224792957305908</v>
       </c>
       <c r="C1144" s="1">
-        <v>-0.10861644893884659</v>
+        <v>-0.42680874466896057</v>
       </c>
     </row>
     <row r="1145">
@@ -10856,7 +10854,7 @@
         <v>0.021739311516284943</v>
       </c>
       <c r="C1145" s="1">
-        <v>0.18267327547073364</v>
+        <v>0.1277851015329361</v>
       </c>
     </row>
     <row r="1146">
@@ -10867,7 +10865,7 @@
         <v>-0.40095669031143188</v>
       </c>
       <c r="C1146" s="1">
-        <v>-0.5223044753074646</v>
+        <v>-0.8110426664352417</v>
       </c>
     </row>
     <row r="1147">
@@ -10878,7 +10876,7 @@
         <v>-0.0060183736495673656</v>
       </c>
       <c r="C1147" s="1">
-        <v>0.12103210389614105</v>
+        <v>0.1536116749048233</v>
       </c>
     </row>
     <row r="1148">
@@ -10889,7 +10887,7 @@
         <v>0.01589558832347393</v>
       </c>
       <c r="C1148" s="1">
-        <v>-0.26685377955436707</v>
+        <v>-0.40618398785591125</v>
       </c>
     </row>
     <row r="1149">
@@ -10900,7 +10898,7 @@
         <v>-0.6463930606842041</v>
       </c>
       <c r="C1149" s="1">
-        <v>0.090701907873153687</v>
+        <v>0.050405167043209076</v>
       </c>
     </row>
     <row r="1150">
@@ -10911,7 +10909,7 @@
         <v>-0.10828353464603424</v>
       </c>
       <c r="C1150" s="1">
-        <v>-0.030731746926903725</v>
+        <v>0.11803515255451202</v>
       </c>
     </row>
     <row r="1151">
@@ -10922,7 +10920,7 @@
         <v>-0.057637929916381836</v>
       </c>
       <c r="C1151" s="1">
-        <v>0.34788268804550171</v>
+        <v>0.32328429818153381</v>
       </c>
     </row>
     <row r="1152">
@@ -10933,7 +10931,7 @@
         <v>-0.94783186912536621</v>
       </c>
       <c r="C1152" s="1">
-        <v>0.23690567910671234</v>
+        <v>0.17504793405532837</v>
       </c>
     </row>
     <row r="1153">
@@ -10944,7 +10942,7 @@
         <v>-0.57626837491989136</v>
       </c>
       <c r="C1153" s="1">
-        <v>1.9070231914520264</v>
+        <v>1.0808912515640259</v>
       </c>
     </row>
     <row r="1154">
@@ -10955,7 +10953,7 @@
         <v>-0.50029999017715454</v>
       </c>
       <c r="C1154" s="1">
-        <v>0.26005876064300537</v>
+        <v>0.55056065320968628</v>
       </c>
     </row>
     <row r="1155">
@@ -10966,7 +10964,7 @@
         <v>-0.22613196074962616</v>
       </c>
       <c r="C1155" s="1">
-        <v>-0.21439938247203827</v>
+        <v>-0.0089587625116109848</v>
       </c>
     </row>
     <row r="1156">
@@ -10977,7 +10975,7 @@
         <v>-0.31719663739204407</v>
       </c>
       <c r="C1156" s="1">
-        <v>0.098776690661907196</v>
+        <v>0.27129283547401428</v>
       </c>
     </row>
     <row r="1157">
@@ -10988,7 +10986,7 @@
         <v>-0.73307490348815918</v>
       </c>
       <c r="C1157" s="1">
-        <v>0.011494318023324013</v>
+        <v>0.056659702211618424</v>
       </c>
     </row>
     <row r="1158">
@@ -10999,7 +10997,7 @@
         <v>0.23893105983734131</v>
       </c>
       <c r="C1158" s="1">
-        <v>0.79153275489807129</v>
+        <v>-0.16231805086135864</v>
       </c>
     </row>
     <row r="1159">
@@ -11010,7 +11008,7 @@
         <v>1.2167806625366211</v>
       </c>
       <c r="C1159" s="1">
-        <v>0.64818114042282104</v>
+        <v>-0.30283018946647644</v>
       </c>
     </row>
     <row r="1160">
@@ -11021,7 +11019,7 @@
         <v>0.10452538728713989</v>
       </c>
       <c r="C1160" s="1">
-        <v>-0.45194411277770996</v>
+        <v>-0.34583374857902527</v>
       </c>
     </row>
     <row r="1161">
@@ -11032,7 +11030,7 @@
         <v>-0.21882730722427368</v>
       </c>
       <c r="C1161" s="1">
-        <v>-0.25058600306510925</v>
+        <v>-0.29919397830963135</v>
       </c>
     </row>
     <row r="1162">
@@ -11043,7 +11041,7 @@
         <v>0.025148153305053711</v>
       </c>
       <c r="C1162" s="1">
-        <v>-0.024669768288731575</v>
+        <v>0.29879593849182129</v>
       </c>
     </row>
     <row r="1163">
@@ -11054,7 +11052,7 @@
         <v>0.36018830537796021</v>
       </c>
       <c r="C1163" s="1">
-        <v>-0.26974570751190186</v>
+        <v>-0.30640998482704163</v>
       </c>
     </row>
     <row r="1164">
@@ -11065,7 +11063,7 @@
         <v>0.074819810688495636</v>
       </c>
       <c r="C1164" s="1">
-        <v>-0.04160139337182045</v>
+        <v>-0.021197719499468803</v>
       </c>
     </row>
     <row r="1165">
@@ -11073,10 +11071,10 @@
         <v>200910</v>
       </c>
       <c r="B1165" s="1">
-        <v>-0.39511296153068542</v>
+        <v>-0.39511296153068543</v>
       </c>
       <c r="C1165" s="1">
-        <v>-0.41317951679229736</v>
+        <v>-0.17763069272041321</v>
       </c>
     </row>
     <row r="1166">
@@ -11087,7 +11085,7 @@
         <v>0.071897931396961212</v>
       </c>
       <c r="C1166" s="1">
-        <v>-0.17646007239818573</v>
+        <v>-0.13821525871753693</v>
       </c>
     </row>
     <row r="1167">
@@ -11098,7 +11096,7 @@
         <v>0.23211334645748138</v>
       </c>
       <c r="C1167" s="1">
-        <v>0.41426187753677368</v>
+        <v>0.52575427293777466</v>
       </c>
     </row>
     <row r="1168">
@@ -11109,7 +11107,7 @@
         <v>0.16101470589637756</v>
       </c>
       <c r="C1168" s="1">
-        <v>-0.19969998300075531</v>
+        <v>-0.19226764142513275</v>
       </c>
     </row>
     <row r="1169">
@@ -11120,7 +11118,7 @@
         <v>-0.086856551468372345</v>
       </c>
       <c r="C1169" s="1">
-        <v>0.53061538934707642</v>
+        <v>0.57122772932052612</v>
       </c>
     </row>
     <row r="1170">
@@ -11131,7 +11129,7 @@
         <v>0.51212513446807861</v>
       </c>
       <c r="C1170" s="1">
-        <v>0.075563833117485046</v>
+        <v>-0.023941623046994209</v>
       </c>
     </row>
     <row r="1171">
@@ -11142,7 +11140,7 @@
         <v>-0.22515800595283508</v>
       </c>
       <c r="C1171" s="1">
-        <v>0.12003688514232635</v>
+        <v>0.104047492146492</v>
       </c>
     </row>
     <row r="1172">
@@ -11153,7 +11151,7 @@
         <v>-0.34885013103485107</v>
       </c>
       <c r="C1172" s="1">
-        <v>0.58392322063446045</v>
+        <v>0.78982949256896973</v>
       </c>
     </row>
     <row r="1173">
@@ -11164,7 +11162,7 @@
         <v>-0.2607073187828064</v>
       </c>
       <c r="C1173" s="1">
-        <v>-0.025814171880483627</v>
+        <v>0.01650969497859478</v>
       </c>
     </row>
     <row r="1174">
@@ -11175,7 +11173,7 @@
         <v>0.24428778886795044</v>
       </c>
       <c r="C1174" s="1">
-        <v>-0.22573304176330566</v>
+        <v>0.098842449486255646</v>
       </c>
     </row>
     <row r="1175">
@@ -11186,7 +11184,7 @@
         <v>-0.13458028435707092</v>
       </c>
       <c r="C1175" s="1">
-        <v>-0.10575589537620544</v>
+        <v>-0.21741525828838348</v>
       </c>
     </row>
     <row r="1176">
@@ -11197,7 +11195,7 @@
         <v>0.37333667278289795</v>
       </c>
       <c r="C1176" s="1">
-        <v>-0.064375698566436768</v>
+        <v>-0.17721439898014069</v>
       </c>
     </row>
     <row r="1177">
@@ -11208,7 +11206,7 @@
         <v>0.027096057310700417</v>
       </c>
       <c r="C1177" s="1">
-        <v>-0.57683521509170532</v>
+        <v>-0.70553380250930786</v>
       </c>
     </row>
     <row r="1178">
@@ -11219,7 +11217,7 @@
         <v>-0.14772866666316986</v>
       </c>
       <c r="C1178" s="1">
-        <v>0.21258029341697693</v>
+        <v>0.23870591819286346</v>
       </c>
     </row>
     <row r="1179">
@@ -11230,7 +11228,7 @@
         <v>0.3626231849193573</v>
       </c>
       <c r="C1179" s="1">
-        <v>0.0058006094768643379</v>
+        <v>-0.043784357607364655</v>
       </c>
     </row>
     <row r="1180">
@@ -11241,7 +11239,7 @@
         <v>0.022713271901011467</v>
       </c>
       <c r="C1180" s="1">
-        <v>-0.041655283421278</v>
+        <v>-0.090422801673412323</v>
       </c>
     </row>
     <row r="1181">
@@ -11252,7 +11250,7 @@
         <v>-0.25583755970001221</v>
       </c>
       <c r="C1181" s="1">
-        <v>-0.10110727697610855</v>
+        <v>-0.24755144119262695</v>
       </c>
     </row>
     <row r="1182">
@@ -11263,7 +11261,7 @@
         <v>0.048523042351007462</v>
       </c>
       <c r="C1182" s="1">
-        <v>-0.46239796280860901</v>
+        <v>-0.62502962350845337</v>
       </c>
     </row>
     <row r="1183">
@@ -11274,7 +11272,7 @@
         <v>0.060697466135025024</v>
       </c>
       <c r="C1183" s="1">
-        <v>0.11907784640789032</v>
+        <v>0.14991597831249237</v>
       </c>
     </row>
     <row r="1184">
@@ -11285,7 +11283,7 @@
         <v>-0.27921244502067566</v>
       </c>
       <c r="C1184" s="1">
-        <v>0.031120851635932922</v>
+        <v>0.10430755466222763</v>
       </c>
     </row>
     <row r="1185">
@@ -11296,7 +11294,7 @@
         <v>-0.32839709520339966</v>
       </c>
       <c r="C1185" s="1">
-        <v>-0.21238747239112854</v>
+        <v>-0.25440871715545654</v>
       </c>
     </row>
     <row r="1186">
@@ -11307,7 +11305,7 @@
         <v>-0.49153438210487366</v>
       </c>
       <c r="C1186" s="1">
-        <v>0.23802608251571655</v>
+        <v>0.45558086037635803</v>
       </c>
     </row>
     <row r="1187">
@@ -11318,7 +11316,7 @@
         <v>-0.34251943230628967</v>
       </c>
       <c r="C1187" s="1">
-        <v>0.081732466816902161</v>
+        <v>0.032303303480148315</v>
       </c>
     </row>
     <row r="1188">
@@ -11329,7 +11327,7 @@
         <v>-0.48130786418914795</v>
       </c>
       <c r="C1188" s="1">
-        <v>0.25711295008659363</v>
+        <v>0.22489133477210999</v>
       </c>
     </row>
     <row r="1189">
@@ -11340,7 +11338,7 @@
         <v>0.38891994953155518</v>
       </c>
       <c r="C1189" s="1">
-        <v>-0.0029631888028234243</v>
+        <v>0.004976681899279356</v>
       </c>
     </row>
     <row r="1190">
@@ -11351,7 +11349,7 @@
         <v>-0.18279100954532623</v>
       </c>
       <c r="C1190" s="1">
-        <v>0.26230183243751526</v>
+        <v>0.3555959165096283</v>
       </c>
     </row>
     <row r="1191">
@@ -11362,7 +11360,7 @@
         <v>-0.26119431853294373</v>
       </c>
       <c r="C1191" s="1">
-        <v>-0.078649424016475677</v>
+        <v>0.012486698105931282</v>
       </c>
     </row>
     <row r="1192">
@@ -11373,7 +11371,7 @@
         <v>0.33876129984855652</v>
       </c>
       <c r="C1192" s="1">
-        <v>0.20925472676753998</v>
+        <v>0.10928686708211899</v>
       </c>
     </row>
     <row r="1193">
@@ -11384,7 +11382,7 @@
         <v>0.24915754795074463</v>
       </c>
       <c r="C1193" s="1">
-        <v>-0.067716717720031738</v>
+        <v>-0.18336233496665955</v>
       </c>
     </row>
     <row r="1194">
@@ -11395,7 +11393,7 @@
         <v>-0.048872344195842743</v>
       </c>
       <c r="C1194" s="1">
-        <v>-0.2076934278011322</v>
+        <v>-0.27974990010261536</v>
       </c>
     </row>
     <row r="1195">
@@ -11406,7 +11404,7 @@
         <v>-0.24658498167991638</v>
       </c>
       <c r="C1195" s="1">
-        <v>0.12648089230060577</v>
+        <v>0.10107421875</v>
       </c>
     </row>
     <row r="1196">
@@ -11417,7 +11415,7 @@
         <v>-0.60694789886474609</v>
       </c>
       <c r="C1196" s="1">
-        <v>0.24711354076862335</v>
+        <v>0.35849499702453613</v>
       </c>
     </row>
     <row r="1197">
@@ -11428,7 +11426,7 @@
         <v>0.018330473452806473</v>
       </c>
       <c r="C1197" s="1">
-        <v>0.12035423517227173</v>
+        <v>0.20398209989070892</v>
       </c>
     </row>
     <row r="1198">
@@ -11439,7 +11437,7 @@
         <v>0.074332833290100098</v>
       </c>
       <c r="C1198" s="1">
-        <v>0.11861293017864227</v>
+        <v>0.29861682653427124</v>
       </c>
     </row>
     <row r="1199">
@@ -11450,7 +11448,7 @@
         <v>0.057775609195232391</v>
       </c>
       <c r="C1199" s="1">
-        <v>-0.29553404450416565</v>
+        <v>-0.30476844310760498</v>
       </c>
     </row>
     <row r="1200">
@@ -11461,7 +11459,7 @@
         <v>0.063619330525398254</v>
       </c>
       <c r="C1200" s="1">
-        <v>-0.19311158359050751</v>
+        <v>-0.27155938744544983</v>
       </c>
     </row>
     <row r="1201">
@@ -11472,7 +11470,7 @@
         <v>0.029530948027968407</v>
       </c>
       <c r="C1201" s="1">
-        <v>0.029299622401595116</v>
+        <v>0.070740848779678345</v>
       </c>
     </row>
     <row r="1202">
@@ -11483,7 +11481,7 @@
         <v>0.099655628204345703</v>
       </c>
       <c r="C1202" s="1">
-        <v>-0.11397687345743179</v>
+        <v>0.088612399995326996</v>
       </c>
     </row>
     <row r="1203">
@@ -11494,7 +11492,7 @@
         <v>0.060210488736629486</v>
       </c>
       <c r="C1203" s="1">
-        <v>-0.051238387823104858</v>
+        <v>-0.015889396890997887</v>
       </c>
     </row>
     <row r="1204">
@@ -11505,7 +11503,7 @@
         <v>0.16344960033893585</v>
       </c>
       <c r="C1204" s="1">
-        <v>-0.47287601232528687</v>
+        <v>-0.4037611186504364</v>
       </c>
     </row>
     <row r="1205">
@@ -11516,7 +11514,7 @@
         <v>0.084072358906269073</v>
       </c>
       <c r="C1205" s="1">
-        <v>-0.017817096784710884</v>
+        <v>-0.1413910835981369</v>
       </c>
     </row>
     <row r="1206">
@@ -11527,7 +11525,7 @@
         <v>-0.062994681298732758</v>
       </c>
       <c r="C1206" s="1">
-        <v>0.26762345433235168</v>
+        <v>0.22540411353111267</v>
       </c>
     </row>
     <row r="1207">
@@ -11538,7 +11536,7 @@
         <v>0.056801654398441315</v>
       </c>
       <c r="C1207" s="1">
-        <v>0.029167545959353447</v>
+        <v>0.075600646436214447</v>
       </c>
     </row>
     <row r="1208">
@@ -11549,7 +11547,7 @@
         <v>0.030504899099469185</v>
       </c>
       <c r="C1208" s="1">
-        <v>-0.11914115399122238</v>
+        <v>-0.048108186572790146</v>
       </c>
     </row>
     <row r="1209">
@@ -11560,7 +11558,7 @@
         <v>-0.29917851090431213</v>
       </c>
       <c r="C1209" s="1">
-        <v>0.22475959360599518</v>
+        <v>0.35780346393585205</v>
       </c>
     </row>
     <row r="1210">
@@ -11571,7 +11569,7 @@
         <v>0.11183005571365356</v>
       </c>
       <c r="C1210" s="1">
-        <v>-0.10871522128582001</v>
+        <v>-0.018491130322217941</v>
       </c>
     </row>
     <row r="1211">
@@ -11582,7 +11580,7 @@
         <v>0.074332833290100098</v>
       </c>
       <c r="C1211" s="1">
-        <v>-0.34887287020683289</v>
+        <v>-0.24294029176235199</v>
       </c>
     </row>
     <row r="1212">
@@ -11593,7 +11591,7 @@
         <v>0.43956553936004639</v>
       </c>
       <c r="C1212" s="1">
-        <v>-0.1088993102312088</v>
+        <v>-0.1472640335559845</v>
       </c>
     </row>
     <row r="1213">
@@ -11604,7 +11602,7 @@
         <v>0.1171867847442627</v>
       </c>
       <c r="C1213" s="1">
-        <v>-0.12299412488937378</v>
+        <v>-0.09772588312625885</v>
       </c>
     </row>
     <row r="1214">
@@ -11615,7 +11613,7 @@
         <v>0.096733763813972473</v>
       </c>
       <c r="C1214" s="1">
-        <v>-0.24119257926940918</v>
+        <v>-0.12148508429527283</v>
       </c>
     </row>
     <row r="1215">
@@ -11626,7 +11624,7 @@
         <v>-0.042541645467281342</v>
       </c>
       <c r="C1215" s="1">
-        <v>0.062899060547351837</v>
+        <v>0.030312301591038704</v>
       </c>
     </row>
     <row r="1216">
@@ -11637,7 +11635,7 @@
         <v>-0.2519417405128479</v>
       </c>
       <c r="C1216" s="1">
-        <v>0.045048151165246964</v>
+        <v>0.15945857763290405</v>
       </c>
     </row>
     <row r="1217">
@@ -11648,7 +11646,7 @@
         <v>0.31149062514305115</v>
       </c>
       <c r="C1217" s="1">
-        <v>-0.2298063337802887</v>
+        <v>-0.25131750106811523</v>
       </c>
     </row>
     <row r="1218">
@@ -11656,10 +11654,10 @@
         <v>201403</v>
       </c>
       <c r="B1218" s="1">
-        <v>-0.1331193596124649</v>
+        <v>-0.13311935961246491</v>
       </c>
       <c r="C1218" s="1">
-        <v>-0.12681600451469421</v>
+        <v>-0.13665090501308441</v>
       </c>
     </row>
     <row r="1219">
@@ -11670,7 +11668,7 @@
         <v>0.064593292772769928</v>
       </c>
       <c r="C1219" s="1">
-        <v>0.14501833915710449</v>
+        <v>0.19975927472114563</v>
       </c>
     </row>
     <row r="1220">
@@ -11681,7 +11679,7 @@
         <v>0.13861379027366638</v>
       </c>
       <c r="C1220" s="1">
-        <v>-0.08234068751335144</v>
+        <v>0.094684064388275147</v>
       </c>
     </row>
     <row r="1221">
@@ -11692,7 +11690,7 @@
         <v>-0.059585839509963989</v>
       </c>
       <c r="C1221" s="1">
-        <v>0.0038236456457525492</v>
+        <v>0.072346650063991547</v>
       </c>
     </row>
     <row r="1222">
@@ -11703,7 +11701,7 @@
         <v>-0.048385370522737503</v>
       </c>
       <c r="C1222" s="1">
-        <v>0.27913129329681396</v>
+        <v>0.44190984964370728</v>
       </c>
     </row>
     <row r="1223">
@@ -11714,7 +11712,7 @@
         <v>-0.0094272112473845482</v>
       </c>
       <c r="C1223" s="1">
-        <v>-0.078553646802902222</v>
+        <v>-0.048178207129240036</v>
       </c>
     </row>
     <row r="1224">
@@ -11725,7 +11723,7 @@
         <v>-0.036210943013429642</v>
       </c>
       <c r="C1224" s="1">
-        <v>0.083056606352329254</v>
+        <v>-0.0060966336168348789</v>
       </c>
     </row>
     <row r="1225">
@@ -11733,10 +11731,10 @@
         <v>201410</v>
       </c>
       <c r="B1225" s="1">
-        <v>-0.054716069251298904</v>
+        <v>-0.054716069251298905</v>
       </c>
       <c r="C1225" s="1">
-        <v>0.072505027055740356</v>
+        <v>0.23612652719020844</v>
       </c>
     </row>
     <row r="1226">
@@ -11747,7 +11745,7 @@
         <v>0.10647329688072205</v>
       </c>
       <c r="C1226" s="1">
-        <v>0.16709716618061066</v>
+        <v>0.35366860032081604</v>
       </c>
     </row>
     <row r="1227">
@@ -11758,7 +11756,7 @@
         <v>-0.12484075129032135</v>
       </c>
       <c r="C1227" s="1">
-        <v>0.014194671995937824</v>
+        <v>0.15726269781589508</v>
       </c>
     </row>
     <row r="1228">
@@ -11769,7 +11767,7 @@
         <v>0.37820643186569214</v>
       </c>
       <c r="C1228" s="1">
-        <v>0.65063261985778809</v>
+        <v>1.0868798494338989</v>
       </c>
     </row>
     <row r="1229">
@@ -11780,7 +11778,7 @@
         <v>0.22529569268226624</v>
       </c>
       <c r="C1229" s="1">
-        <v>-0.23587112128734589</v>
+        <v>-0.25771993398666382</v>
       </c>
     </row>
     <row r="1230">
@@ -11791,7 +11789,7 @@
         <v>0.05144491046667099</v>
       </c>
       <c r="C1230" s="1">
-        <v>0.43358278274536133</v>
+        <v>0.46087175607681274</v>
       </c>
     </row>
     <row r="1231">
@@ -11802,7 +11800,7 @@
         <v>-0.2392803430557251</v>
       </c>
       <c r="C1231" s="1">
-        <v>0.0099342577159404755</v>
+        <v>0.10311450809240341</v>
       </c>
     </row>
     <row r="1232">
@@ -11813,7 +11811,7 @@
         <v>0.023200249299407005</v>
       </c>
       <c r="C1232" s="1">
-        <v>-0.20733335614204407</v>
+        <v>-0.113221175968647</v>
       </c>
     </row>
     <row r="1233">
@@ -11824,7 +11822,7 @@
         <v>-0.24025428295135498</v>
       </c>
       <c r="C1233" s="1">
-        <v>0.76886260509490967</v>
+        <v>-0.19916833937168121</v>
       </c>
     </row>
     <row r="1234">
@@ -11835,7 +11833,7 @@
         <v>0.1717282235622406</v>
       </c>
       <c r="C1234" s="1">
-        <v>0.2664637565612793</v>
+        <v>0.4781450629234314</v>
       </c>
     </row>
     <row r="1235">
@@ -11846,7 +11844,7 @@
         <v>-0.45208930969238281</v>
       </c>
       <c r="C1235" s="1">
-        <v>-0.083992436528205872</v>
+        <v>-0.078087016940116882</v>
       </c>
     </row>
     <row r="1236">
@@ -11857,7 +11855,7 @@
         <v>-0.20519194006919861</v>
       </c>
       <c r="C1236" s="1">
-        <v>-0.031521249562501907</v>
+        <v>-0.00079640012700110674</v>
       </c>
     </row>
     <row r="1237">
@@ -11868,7 +11866,7 @@
         <v>0.40839898586273193</v>
       </c>
       <c r="C1237" s="1">
-        <v>-0.13829246163368225</v>
+        <v>-0.11166004836559296</v>
       </c>
     </row>
     <row r="1238">
@@ -11879,7 +11877,7 @@
         <v>0.19802497327327728</v>
       </c>
       <c r="C1238" s="1">
-        <v>0.48855623602867126</v>
+        <v>0.71487349271774292</v>
       </c>
     </row>
     <row r="1239">
@@ -11887,10 +11885,10 @@
         <v>201512</v>
       </c>
       <c r="B1239" s="1">
-        <v>-0.16672076284885406</v>
+        <v>-0.16672076284885407</v>
       </c>
       <c r="C1239" s="1">
-        <v>-0.34646302461624146</v>
+        <v>-0.26031288504600525</v>
       </c>
     </row>
     <row r="1240">
@@ -11901,7 +11899,7 @@
         <v>-0.18230403959751129</v>
       </c>
       <c r="C1240" s="1">
-        <v>0.2294444739818573</v>
+        <v>0.50137192010879517</v>
       </c>
     </row>
     <row r="1241">
@@ -11912,7 +11910,7 @@
         <v>-0.27872547507286072</v>
       </c>
       <c r="C1241" s="1">
-        <v>-0.2336602509021759</v>
+        <v>-0.22653564810752869</v>
       </c>
     </row>
     <row r="1242">
@@ -11923,7 +11921,7 @@
         <v>0.090403065085411072</v>
       </c>
       <c r="C1242" s="1">
-        <v>-0.090364530682563782</v>
+        <v>-0.14446669816970825</v>
       </c>
     </row>
     <row r="1243">
@@ -11934,7 +11932,7 @@
         <v>-0.045463506132364273</v>
       </c>
       <c r="C1243" s="1">
-        <v>-0.10871566832065582</v>
+        <v>-0.14473837614059448</v>
       </c>
     </row>
     <row r="1244">
@@ -11945,7 +11943,7 @@
         <v>0.094298884272575378</v>
       </c>
       <c r="C1244" s="1">
-        <v>0.10884569585323334</v>
+        <v>0.22806507349014282</v>
       </c>
     </row>
     <row r="1245">
@@ -11956,7 +11954,7 @@
         <v>-0.095622137188911438</v>
       </c>
       <c r="C1245" s="1">
-        <v>-0.21354827284812927</v>
+        <v>-0.16695456206798554</v>
       </c>
     </row>
     <row r="1246">
@@ -11967,7 +11965,7 @@
         <v>0.23600916564464569</v>
       </c>
       <c r="C1246" s="1">
-        <v>0.15197041630744934</v>
+        <v>0.29205548763275147</v>
       </c>
     </row>
     <row r="1247">
@@ -11978,7 +11976,7 @@
         <v>-0.042541645467281342</v>
       </c>
       <c r="C1247" s="1">
-        <v>0.11074915528297424</v>
+        <v>0.19847391545772553</v>
       </c>
     </row>
     <row r="1248">
@@ -11989,7 +11987,7 @@
         <v>0.085046306252479553</v>
       </c>
       <c r="C1248" s="1">
-        <v>-0.066070787608623505</v>
+        <v>-0.044332925230264664</v>
       </c>
     </row>
     <row r="1249">
@@ -12000,7 +11998,7 @@
         <v>-0.1545463502407074</v>
       </c>
       <c r="C1249" s="1">
-        <v>-0.081615403294563293</v>
+        <v>-0.076831445097923279</v>
       </c>
     </row>
     <row r="1250">
@@ -12011,7 +12009,7 @@
         <v>-0.028906293213367462</v>
       </c>
       <c r="C1250" s="1">
-        <v>0.050555914640426636</v>
+        <v>0.14493617415428162</v>
       </c>
     </row>
     <row r="1251">
@@ -12022,7 +12020,7 @@
         <v>0.19948588311672211</v>
       </c>
       <c r="C1251" s="1">
-        <v>0.43492108583450317</v>
+        <v>0.49517503380775452</v>
       </c>
     </row>
     <row r="1252">
@@ -12033,7 +12031,7 @@
         <v>-0.13993702828884125</v>
       </c>
       <c r="C1252" s="1">
-        <v>-0.26388421654701233</v>
+        <v>0.011405786499381065</v>
       </c>
     </row>
     <row r="1253">
@@ -12044,7 +12042,7 @@
         <v>0.098194688558578491</v>
       </c>
       <c r="C1253" s="1">
-        <v>-0.088721856474876404</v>
+        <v>-0.18921773135662079</v>
       </c>
     </row>
     <row r="1254">
@@ -12055,7 +12053,7 @@
         <v>0.10452538728713989</v>
       </c>
       <c r="C1254" s="1">
-        <v>0.011490521021187305</v>
+        <v>0.11110666394233704</v>
       </c>
     </row>
     <row r="1255">
@@ -12066,7 +12064,7 @@
         <v>0.18487660586833954</v>
       </c>
       <c r="C1255" s="1">
-        <v>-0.20215880870819092</v>
+        <v>-0.24389919638633728</v>
       </c>
     </row>
     <row r="1256">
@@ -12077,7 +12075,7 @@
         <v>0.075793758034706116</v>
       </c>
       <c r="C1256" s="1">
-        <v>-0.15173418819904327</v>
+        <v>-0.023861341178417206</v>
       </c>
     </row>
     <row r="1257">
@@ -12088,7 +12086,7 @@
         <v>-0.099030971527099609</v>
       </c>
       <c r="C1257" s="1">
-        <v>-0.18179813027381897</v>
+        <v>-0.1441836804151535</v>
       </c>
     </row>
     <row r="1258">
@@ -12099,7 +12097,7 @@
         <v>-0.10341376066207886</v>
       </c>
       <c r="C1258" s="1">
-        <v>-0.078147873282432556</v>
+        <v>0.10283790528774261</v>
       </c>
     </row>
     <row r="1259">
@@ -12110,7 +12108,7 @@
         <v>-0.04643746092915535</v>
       </c>
       <c r="C1259" s="1">
-        <v>-0.15789370238780975</v>
+        <v>-0.1804540753364563</v>
       </c>
     </row>
     <row r="1260">
@@ -12121,7 +12119,7 @@
         <v>0.040244430303573608</v>
       </c>
       <c r="C1260" s="1">
-        <v>-0.3276781439781189</v>
+        <v>-0.3495384156703949</v>
       </c>
     </row>
     <row r="1261">
@@ -12132,7 +12130,7 @@
         <v>-0.030854199081659317</v>
       </c>
       <c r="C1261" s="1">
-        <v>0.31531825661659241</v>
+        <v>0.45080763101577759</v>
       </c>
     </row>
     <row r="1262">
@@ -12143,7 +12141,7 @@
         <v>-0.15259842574596405</v>
       </c>
       <c r="C1262" s="1">
-        <v>0.048055846244096756</v>
+        <v>0.051402047276496887</v>
       </c>
     </row>
     <row r="1263">
@@ -12154,7 +12152,7 @@
         <v>-0.05276816338300705</v>
       </c>
       <c r="C1263" s="1">
-        <v>-0.45438575744628906</v>
+        <v>-0.40429198741912842</v>
       </c>
     </row>
     <row r="1264">
@@ -12165,7 +12163,7 @@
         <v>0.07238490879535675</v>
       </c>
       <c r="C1264" s="1">
-        <v>-0.12060857564210892</v>
+        <v>0.062586203217506409</v>
       </c>
     </row>
     <row r="1265">
@@ -12176,7 +12174,7 @@
         <v>0.073358863592147827</v>
       </c>
       <c r="C1265" s="1">
-        <v>-0.093294061720371246</v>
+        <v>-0.12418986111879349</v>
       </c>
     </row>
     <row r="1266">
@@ -12187,7 +12185,7 @@
         <v>-0.14383284747600555</v>
       </c>
       <c r="C1266" s="1">
-        <v>0.0029127912130206823</v>
+        <v>0.015233923681080341</v>
       </c>
     </row>
     <row r="1267">
@@ -12198,7 +12196,7 @@
         <v>0.24087895452976227</v>
       </c>
       <c r="C1267" s="1">
-        <v>0.27849346399307251</v>
+        <v>0.32401928305625916</v>
       </c>
     </row>
     <row r="1268">
@@ -12209,7 +12207,7 @@
         <v>0.030504899099469185</v>
       </c>
       <c r="C1268" s="1">
-        <v>0.37995633482933044</v>
+        <v>0.47826129198074341</v>
       </c>
     </row>
     <row r="1269">
@@ -12220,7 +12218,7 @@
         <v>-0.11120539158582687</v>
       </c>
       <c r="C1269" s="1">
-        <v>0.20181049406528473</v>
+        <v>0.23521415889263153</v>
       </c>
     </row>
     <row r="1270">
@@ -12231,7 +12229,7 @@
         <v>-0.019166754558682442</v>
       </c>
       <c r="C1270" s="1">
-        <v>-0.085079140961170197</v>
+        <v>0.030388442799448967</v>
       </c>
     </row>
     <row r="1271">
@@ -12239,10 +12237,10 @@
         <v>201808</v>
       </c>
       <c r="B1271" s="1">
-        <v>0.049983981996774673</v>
+        <v>0.049983981996774674</v>
       </c>
       <c r="C1271" s="1">
-        <v>-0.012022671289741993</v>
+        <v>0.027433121576905251</v>
       </c>
     </row>
     <row r="1272">
@@ -12253,7 +12251,7 @@
         <v>-0.098543994128704071</v>
       </c>
       <c r="C1272" s="1">
-        <v>0.00736657390370965</v>
+        <v>0.015169959515333176</v>
       </c>
     </row>
     <row r="1273">
@@ -12264,7 +12262,7 @@
         <v>-0.40582644939422607</v>
       </c>
       <c r="C1273" s="1">
-        <v>0.099273383617401123</v>
+        <v>0.11114506423473358</v>
       </c>
     </row>
     <row r="1274">
@@ -12275,7 +12273,7 @@
         <v>-0.24804592132568359</v>
       </c>
       <c r="C1274" s="1">
-        <v>0.12690059840679169</v>
+        <v>0.23786236345767975</v>
       </c>
     </row>
     <row r="1275">
@@ -12286,7 +12284,7 @@
         <v>-0.17694728076457977</v>
       </c>
       <c r="C1275" s="1">
-        <v>0.43338143825531006</v>
+        <v>0.61321353912353516</v>
       </c>
     </row>
     <row r="1276">
@@ -12297,7 +12295,7 @@
         <v>0.33924826979637146</v>
       </c>
       <c r="C1276" s="1">
-        <v>-0.42532685399055481</v>
+        <v>-0.23496024310588837</v>
       </c>
     </row>
     <row r="1277">
@@ -12308,7 +12306,7 @@
         <v>0.068489104509353638</v>
       </c>
       <c r="C1277" s="1">
-        <v>-0.16416585445404053</v>
+        <v>-0.26181143522262573</v>
       </c>
     </row>
     <row r="1278">
@@ -12319,7 +12317,7 @@
         <v>0.0256351288408041</v>
       </c>
       <c r="C1278" s="1">
-        <v>0.24729627370834351</v>
+        <v>0.34419944882392883</v>
       </c>
     </row>
     <row r="1279">
@@ -12330,7 +12328,7 @@
         <v>0.017356522381305695</v>
       </c>
       <c r="C1279" s="1">
-        <v>-0.33511835336685181</v>
+        <v>-0.49713596701622009</v>
       </c>
     </row>
     <row r="1280">
@@ -12341,7 +12339,7 @@
         <v>-0.24658498167991638</v>
       </c>
       <c r="C1280" s="1">
-        <v>0.23934297263622284</v>
+        <v>0.42226773500442505</v>
       </c>
     </row>
     <row r="1281">
@@ -12352,7 +12350,7 @@
         <v>0.1551709920167923</v>
       </c>
       <c r="C1281" s="1">
-        <v>0.094951331615447998</v>
+        <v>0.17207562923431396</v>
       </c>
     </row>
     <row r="1282">
@@ -12363,7 +12361,7 @@
         <v>-0.068351425230503082</v>
       </c>
       <c r="C1282" s="1">
-        <v>-0.10791473835706711</v>
+        <v>0.069496944546699524</v>
       </c>
     </row>
     <row r="1283">
@@ -12374,7 +12372,7 @@
         <v>-0.14334587752819061</v>
       </c>
       <c r="C1283" s="1">
-        <v>-0.14223888516426086</v>
+        <v>-0.2155238687992096</v>
       </c>
     </row>
     <row r="1284">
@@ -12385,7 +12383,7 @@
         <v>0.13520495593547821</v>
       </c>
       <c r="C1284" s="1">
-        <v>0.16818886995315552</v>
+        <v>0.26935786008834839</v>
       </c>
     </row>
     <row r="1285">
@@ -12396,7 +12394,7 @@
         <v>-0.026471406221389771</v>
       </c>
       <c r="C1285" s="1">
-        <v>-0.12039443105459213</v>
+        <v>-0.07030787318944931</v>
       </c>
     </row>
     <row r="1286">
@@ -12404,10 +12402,10 @@
         <v>201911</v>
       </c>
       <c r="B1286" s="1">
-        <v>-0.054716069251298904</v>
+        <v>-0.054716069251298905</v>
       </c>
       <c r="C1286" s="1">
-        <v>-0.010966908186674118</v>
+        <v>0.11441019177436829</v>
       </c>
     </row>
     <row r="1287">
@@ -12418,7 +12416,7 @@
         <v>0.092350967228412628</v>
       </c>
       <c r="C1287" s="1">
-        <v>0.099586032330989838</v>
+        <v>0.15921604633331299</v>
       </c>
     </row>
     <row r="1288">
@@ -12429,7 +12427,7 @@
         <v>0.082611426711082458</v>
       </c>
       <c r="C1288" s="1">
-        <v>-0.12896411120891571</v>
+        <v>0.068025834858417511</v>
       </c>
     </row>
     <row r="1289">
@@ -12440,7 +12438,7 @@
         <v>-0.38391250371932983</v>
       </c>
       <c r="C1289" s="1">
-        <v>0.21067239344120026</v>
+        <v>0.19972848892211914</v>
       </c>
     </row>
     <row r="1290">
@@ -12451,7 +12449,7 @@
         <v>-0.78274661302566528</v>
       </c>
       <c r="C1290" s="1">
-        <v>-0.15208818018436432</v>
+        <v>-0.034562088549137115</v>
       </c>
     </row>
     <row r="1291">
@@ -12462,7 +12460,7 @@
         <v>0.48290649056434631</v>
       </c>
       <c r="C1291" s="1">
-        <v>-0.052188199013471603</v>
+        <v>0.17254981398582458</v>
       </c>
     </row>
     <row r="1292">
@@ -12473,7 +12471,7 @@
         <v>0.31733432412147522</v>
       </c>
       <c r="C1292" s="1">
-        <v>-0.58072394132614136</v>
+        <v>-0.54040366411209107</v>
       </c>
     </row>
     <row r="1293">
@@ -12484,7 +12482,7 @@
         <v>-0.058124907314777374</v>
       </c>
       <c r="C1293" s="1">
-        <v>0.050762839615345001</v>
+        <v>0.072274342179298401</v>
       </c>
     </row>
     <row r="1294">
@@ -12495,7 +12493,7 @@
         <v>0.15711890161037445</v>
       </c>
       <c r="C1294" s="1">
-        <v>-0.448301762342453</v>
+        <v>-0.54126769304275513</v>
       </c>
     </row>
     <row r="1295">
@@ -12506,7 +12504,7 @@
         <v>0.26279288530349731</v>
       </c>
       <c r="C1295" s="1">
-        <v>-0.5219956636428833</v>
+        <v>-0.49854147434234619</v>
       </c>
     </row>
     <row r="1296">
@@ -12517,7 +12515,7 @@
         <v>-0.051307231187820435</v>
       </c>
       <c r="C1296" s="1">
-        <v>1.2979730367660522</v>
+        <v>0.40094152092933655</v>
       </c>
     </row>
     <row r="1297">
@@ -12528,7 +12526,7 @@
         <v>-0.26216825842857361</v>
       </c>
       <c r="C1297" s="1">
-        <v>-0.058014765381813049</v>
+        <v>-0.015007514506578445</v>
       </c>
     </row>
     <row r="1298">
@@ -12539,7 +12537,7 @@
         <v>0.50676840543746948</v>
       </c>
       <c r="C1298" s="1">
-        <v>-0.062975935637950897</v>
+        <v>0.053646203130483627</v>
       </c>
     </row>
     <row r="1299">
@@ -12550,7 +12548,7 @@
         <v>0.059723511338233948</v>
       </c>
       <c r="C1299" s="1">
-        <v>-0.28493309020996094</v>
+        <v>-0.27874559164047241</v>
       </c>
     </row>
     <row r="1300">
@@ -12558,10 +12556,10 @@
         <v>202101</v>
       </c>
       <c r="B1300" s="1">
-        <v>0.049983981996774673</v>
+        <v>0.049983981996774674</v>
       </c>
       <c r="C1300" s="1">
-        <v>-0.081953190267086029</v>
+        <v>-0.12276538461446762</v>
       </c>
     </row>
     <row r="1301">
@@ -12572,7 +12570,7 @@
         <v>-0.060559794306755066</v>
       </c>
       <c r="C1301" s="1">
-        <v>0.051969703286886215</v>
+        <v>0.013334251008927822</v>
       </c>
     </row>
     <row r="1302">
@@ -12583,7 +12581,7 @@
         <v>0.058262582868337631</v>
       </c>
       <c r="C1302" s="1">
-        <v>0.25856828689575195</v>
+        <v>0.29765599966049194</v>
       </c>
     </row>
     <row r="1303">
@@ -12594,7 +12592,7 @@
         <v>0.19364216923713684</v>
       </c>
       <c r="C1303" s="1">
-        <v>-0.41249993443489075</v>
+        <v>-0.50115048885345459</v>
       </c>
     </row>
     <row r="1304">
@@ -12605,7 +12603,7 @@
         <v>0.033913731575012207</v>
       </c>
       <c r="C1304" s="1">
-        <v>-0.052326448261737823</v>
+        <v>-0.025508521124720573</v>
       </c>
     </row>
     <row r="1305">
@@ -12616,7 +12614,7 @@
         <v>0.040244430303573608</v>
       </c>
       <c r="C1305" s="1">
-        <v>0.28055247664451599</v>
+        <v>0.43014100193977356</v>
       </c>
     </row>
     <row r="1306">
@@ -12627,7 +12625,7 @@
         <v>0.2019207775592804</v>
       </c>
       <c r="C1306" s="1">
-        <v>0.087485209107398987</v>
+        <v>0.073009759187698364</v>
       </c>
     </row>
     <row r="1307">
@@ -12638,7 +12636,7 @@
         <v>-0.0030965122859925032</v>
       </c>
       <c r="C1307" s="1">
-        <v>0.21838347613811493</v>
+        <v>0.24856263399124146</v>
       </c>
     </row>
     <row r="1308">
@@ -12649,7 +12647,7 @@
         <v>-0.42676645517349243</v>
       </c>
       <c r="C1308" s="1">
-        <v>-0.18149702250957489</v>
+        <v>-0.23167502880096436</v>
       </c>
     </row>
     <row r="1309">
@@ -12660,7 +12658,7 @@
         <v>0.044140249490737915</v>
       </c>
       <c r="C1309" s="1">
-        <v>0.37003999948501587</v>
+        <v>0.23222978413105011</v>
       </c>
     </row>
     <row r="1310">
@@ -12671,7 +12669,7 @@
         <v>-0.18035611510276794</v>
       </c>
       <c r="C1310" s="1">
-        <v>0.075934410095214844</v>
+        <v>0.011307992041110992</v>
       </c>
     </row>
     <row r="1311">
@@ -12682,7 +12680,7 @@
         <v>0.19266822934150696</v>
       </c>
       <c r="C1311" s="1">
-        <v>-0.17222891747951508</v>
+        <v>-0.071100488305091858</v>
       </c>
     </row>
     <row r="1312">
@@ -12693,7 +12691,7 @@
         <v>-0.32206642627716064</v>
       </c>
       <c r="C1312" s="1">
-        <v>0.11216131597757339</v>
+        <v>-0.2287323921918869</v>
       </c>
     </row>
     <row r="1313">
@@ -12704,7 +12702,7 @@
         <v>-0.46036788821220398</v>
       </c>
       <c r="C1313" s="1">
-        <v>0.13863952457904816</v>
+        <v>0.048654142767190933</v>
       </c>
     </row>
     <row r="1314">
@@ -12715,7 +12713,7 @@
         <v>0.04170536994934082</v>
       </c>
       <c r="C1314" s="1">
-        <v>0.25435677170753479</v>
+        <v>-0.14377528429031372</v>
       </c>
     </row>
     <row r="1315">
@@ -12726,7 +12724,7 @@
         <v>-0.071760259568691254</v>
       </c>
       <c r="C1315" s="1">
-        <v>0.24345530569553375</v>
+        <v>0.24461172521114349</v>
       </c>
     </row>
     <row r="1316">
@@ -12737,7 +12735,7 @@
         <v>-0.054229091852903366</v>
       </c>
       <c r="C1316" s="1">
-        <v>0.230024054646492</v>
+        <v>-0.123404361307621</v>
       </c>
     </row>
     <row r="1317">
@@ -12748,7 +12746,7 @@
         <v>-0.38147759437561035</v>
       </c>
       <c r="C1317" s="1">
-        <v>-0.37355607748031616</v>
+        <v>-0.59521067142486572</v>
       </c>
     </row>
     <row r="1318">
@@ -12759,7 +12757,7 @@
         <v>0.25646218657493591</v>
       </c>
       <c r="C1318" s="1">
-        <v>0.24195396900177002</v>
+        <v>0.25758016109466553</v>
       </c>
     </row>
     <row r="1319">
@@ -12770,7 +12768,7 @@
         <v>-0.17402543127536774</v>
       </c>
       <c r="C1319" s="1">
-        <v>-0.0088409213349223137</v>
+        <v>0.050652772188186646</v>
       </c>
     </row>
     <row r="1320">
@@ -12781,7 +12779,7 @@
         <v>-0.392191082239151</v>
       </c>
       <c r="C1320" s="1">
-        <v>0.1372356116771698</v>
+        <v>-0.045003041625022888</v>
       </c>
     </row>
     <row r="1321">
@@ -12792,7 +12790,7 @@
         <v>0.14056169986724854</v>
       </c>
       <c r="C1321" s="1">
-        <v>0.40726044774055481</v>
+        <v>0.21473631262779236</v>
       </c>
     </row>
     <row r="1322">
@@ -12803,7 +12801,7 @@
         <v>0.28957664966583252</v>
       </c>
       <c r="C1322" s="1">
-        <v>-0.46241611242294312</v>
+        <v>-0.86457192897796631</v>
       </c>
     </row>
     <row r="1323">
@@ -12814,7 +12812,7 @@
         <v>-0.18668682873249054</v>
       </c>
       <c r="C1323" s="1">
-        <v>-0.63490456342697144</v>
+        <v>-0.60587805509567261</v>
       </c>
     </row>
     <row r="1324">
@@ -12825,7 +12823,7 @@
         <v>0.03927047923207283</v>
       </c>
       <c r="C1324" s="1">
-        <v>-0.05184468999505043</v>
+        <v>-0.17299796640872955</v>
       </c>
     </row>
     <row r="1325">
@@ -12836,7 +12834,7 @@
         <v>-0.0074793063104152679</v>
       </c>
       <c r="C1325" s="1">
-        <v>0.27262648940086365</v>
+        <v>0.094975806772708893</v>
       </c>
     </row>
     <row r="1326">
@@ -12847,7 +12845,7 @@
         <v>-0.14724168181419373</v>
       </c>
       <c r="C1326" s="1">
-        <v>-0.057713106274604797</v>
+        <v>-0.2170703113079071</v>
       </c>
     </row>
     <row r="1327">
@@ -12858,7 +12856,7 @@
         <v>-0.055203046649694443</v>
       </c>
       <c r="C1327" s="1">
-        <v>-0.42519402503967285</v>
+        <v>-0.49651831388473511</v>
       </c>
     </row>
     <row r="1328">
@@ -12869,7 +12867,7 @@
         <v>-0.32157942652702332</v>
       </c>
       <c r="C1328" s="1">
-        <v>0.072111383080482483</v>
+        <v>0.066604942083358765</v>
       </c>
     </row>
     <row r="1329">
@@ -12880,7 +12878,7 @@
         <v>-0.1228928416967392</v>
       </c>
       <c r="C1329" s="1">
-        <v>0.035053901374340057</v>
+        <v>0.061705548316240311</v>
       </c>
     </row>
     <row r="1330">
@@ -12891,7 +12889,7 @@
         <v>-0.1141272634267807</v>
       </c>
       <c r="C1330" s="1">
-        <v>-0.2731931209564209</v>
+        <v>-0.40084806084632874</v>
       </c>
     </row>
     <row r="1331">
@@ -12902,7 +12900,7 @@
         <v>-0.060072816908359528</v>
       </c>
       <c r="C1331" s="1">
-        <v>0.07928457111120224</v>
+        <v>0.44071686267852783</v>
       </c>
     </row>
     <row r="1332">
@@ -12913,7 +12911,7 @@
         <v>-0.18668682873249054</v>
       </c>
       <c r="C1332" s="1">
-        <v>0.15289294719696045</v>
+        <v>0.0065240543335676193</v>
       </c>
     </row>
     <row r="1333">
@@ -12924,7 +12922,7 @@
         <v>-0.23392358422279358</v>
       </c>
       <c r="C1333" s="1">
-        <v>0.079671882092952728</v>
+        <v>0.075272984802722931</v>
       </c>
     </row>
     <row r="1334">
@@ -12935,7 +12933,7 @@
         <v>0.24720963835716248</v>
       </c>
       <c r="C1334" s="1">
-        <v>-0.31311118602752686</v>
+        <v>-0.13572379946708679</v>
       </c>
     </row>
     <row r="1335">
